--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://docs.philips.com/personal/pratibha_mehta_philips_com/Documents/Desktop/DMB-Kavya/DMB-Dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{40CFDC8C-9992-4F76-A9C2-B6000D96F71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F33A1F9-7AE6-4912-A1C0-455E33878DD0}"/>
+  <xr:revisionPtr revIDLastSave="1339" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6F3CF3A-D0D8-4077-8C76-9C30B5420B9F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -859,9 +859,6 @@
     <t>Clear to build material avaialbility</t>
   </si>
   <si>
-    <t>OOH%</t>
-  </si>
-  <si>
     <t>B&amp;B to meet sales AOP</t>
   </si>
   <si>
@@ -1020,21 +1017,6 @@
 (Sec 7 - IQ-PSW signoff)  - SVAL</t>
   </si>
   <si>
-    <t>LCM ::SICR Inflow  vs Outflow</t>
-  </si>
-  <si>
-    <t>SICR burndown [ outflow / inflow &gt; 1 ]</t>
-  </si>
-  <si>
-    <t>&gt;=1</t>
-  </si>
-  <si>
-    <t>LCM :: Production Delay due to delay in CR's</t>
-  </si>
-  <si>
-    <t>Production stops due to delay in CR/SICR</t>
-  </si>
-  <si>
     <t>Critical &amp; MLD Milestone Delivery On-Time (%)</t>
   </si>
   <si>
@@ -1362,6 +1344,24 @@
   </si>
   <si>
     <t>Order Intake CS(Growth)</t>
+  </si>
+  <si>
+    <t>LCM :: Production Delay due to delay in CR's</t>
+  </si>
+  <si>
+    <t>Production stops due to delay in CR/SICR</t>
+  </si>
+  <si>
+    <t>SICR burndown [ outflow / inflow &gt; 1 ]</t>
+  </si>
+  <si>
+    <t>&gt;=1</t>
+  </si>
+  <si>
+    <t>LCM ::SICR Inflow  vs Outflow</t>
+  </si>
+  <si>
+    <t>OOH%</t>
   </si>
 </sst>
 </file>
@@ -1546,7 +1546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1585,6 +1585,10 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2479,19 +2483,19 @@
   <dimension ref="A1:Y59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.1796875" customWidth="1"/>
+    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.81640625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="55.26953125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" hidden="1" customWidth="1"/>
     <col min="5" max="6" width="10.7265625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.453125" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="6.54296875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1796875" hidden="1" customWidth="1"/>
     <col min="11" max="13" width="8.7265625" customWidth="1"/>
     <col min="14" max="14" width="8.1796875" customWidth="1"/>
     <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="17" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5429,14 +5433,13 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="6">
+    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5446,13 +5449,15 @@
   <dimension ref="A1:V200"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.08984375" customWidth="1"/>
-    <col min="2" max="6" width="43.453125" customWidth="1"/>
-    <col min="7" max="11" width="43.453125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="35.54296875" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="11.453125" hidden="1" customWidth="1"/>
+    <col min="1" max="5" width="43.36328125" customWidth="1"/>
+    <col min="6" max="6" width="15.36328125" customWidth="1"/>
+    <col min="7" max="11" width="43.36328125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="35.6328125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.81640625" customWidth="1"/>
-    <col min="16" max="19" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.453125" customWidth="1"/>
+    <col min="17" max="19" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="17.81640625" bestFit="1" customWidth="1"/>
@@ -5639,7 +5644,7 @@
       <c r="N6" s="4">
         <v>0.3</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="39">
         <v>0.4</v>
       </c>
       <c r="P6" s="4">
@@ -5699,7 +5704,7 @@
       <c r="N7">
         <v>4</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="38">
         <v>4</v>
       </c>
       <c r="P7">
@@ -5755,7 +5760,7 @@
       <c r="N8">
         <v>4</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="38">
         <v>4</v>
       </c>
       <c r="P8">
@@ -5811,7 +5816,7 @@
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="38">
         <v>0</v>
       </c>
       <c r="P9">
@@ -5867,7 +5872,7 @@
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="38">
         <v>0</v>
       </c>
       <c r="P10">
@@ -5923,7 +5928,7 @@
       <c r="N11" s="2">
         <v>0.9</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="40">
         <v>0.9</v>
       </c>
       <c r="P11" s="2">
@@ -5983,7 +5988,7 @@
       <c r="N12" s="2">
         <v>0</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="40">
         <v>1</v>
       </c>
       <c r="P12" s="2">
@@ -6043,7 +6048,7 @@
       <c r="N13" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="41">
         <v>0.06</v>
       </c>
       <c r="P13" s="3">
@@ -6103,7 +6108,7 @@
       <c r="N14" s="3">
         <v>0.03</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="41">
         <v>0.03</v>
       </c>
       <c r="P14" s="3">
@@ -7879,16 +7884,16 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" t="s">
         <v>163</v>
-      </c>
-      <c r="B47" t="s">
-        <v>164</v>
       </c>
       <c r="C47" t="s">
         <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E47" t="s">
         <v>60</v>
@@ -7927,16 +7932,16 @@
         <v>0.95</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U47" t="s">
         <v>32</v>
@@ -7947,16 +7952,16 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>326</v>
+      </c>
+      <c r="B48" t="s">
         <v>163</v>
-      </c>
-      <c r="B48" t="s">
-        <v>164</v>
       </c>
       <c r="C48" t="s">
         <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
         <v>60</v>
@@ -7995,16 +8000,16 @@
         <v>0.71</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U48" t="s">
         <v>32</v>
@@ -8015,16 +8020,16 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" t="s">
         <v>167</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>168</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>169</v>
-      </c>
-      <c r="D49" t="s">
-        <v>170</v>
       </c>
       <c r="E49" t="s">
         <v>60</v>
@@ -8073,16 +8078,16 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" t="s">
         <v>167</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>168</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>169</v>
-      </c>
-      <c r="D50" t="s">
-        <v>170</v>
       </c>
       <c r="E50" t="s">
         <v>60</v>
@@ -8131,10 +8136,10 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" t="s">
         <v>171</v>
-      </c>
-      <c r="B51" t="s">
-        <v>172</v>
       </c>
       <c r="C51" t="s">
         <v>122</v>
@@ -8189,10 +8194,10 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" t="s">
         <v>171</v>
-      </c>
-      <c r="B52" t="s">
-        <v>172</v>
       </c>
       <c r="C52" t="s">
         <v>122</v>
@@ -8247,16 +8252,16 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" t="s">
         <v>173</v>
-      </c>
-      <c r="B53" t="s">
-        <v>174</v>
       </c>
       <c r="C53" t="s">
         <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E53" t="s">
         <v>60</v>
@@ -8305,16 +8310,16 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" t="s">
         <v>173</v>
-      </c>
-      <c r="B54" t="s">
-        <v>174</v>
       </c>
       <c r="C54" t="s">
         <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E54" t="s">
         <v>60</v>
@@ -8363,10 +8368,10 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>176</v>
+      </c>
+      <c r="B55" t="s">
         <v>177</v>
-      </c>
-      <c r="B55" t="s">
-        <v>178</v>
       </c>
       <c r="C55" t="s">
         <v>116</v>
@@ -8421,10 +8426,10 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" t="s">
         <v>177</v>
-      </c>
-      <c r="B56" t="s">
-        <v>178</v>
       </c>
       <c r="C56" t="s">
         <v>116</v>
@@ -8479,16 +8484,16 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>178</v>
+      </c>
+      <c r="B57" t="s">
         <v>179</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" t="s">
         <v>180</v>
-      </c>
-      <c r="C57" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" t="s">
-        <v>181</v>
       </c>
       <c r="E57" t="s">
         <v>29</v>
@@ -8537,13 +8542,13 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" t="s">
         <v>179</v>
       </c>
-      <c r="B58" t="s">
-        <v>180</v>
-      </c>
       <c r="C58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E58" t="s">
         <v>29</v>
@@ -8592,10 +8597,10 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" t="s">
         <v>182</v>
-      </c>
-      <c r="B59" t="s">
-        <v>183</v>
       </c>
       <c r="C59" t="s">
         <v>128</v>
@@ -8613,7 +8618,7 @@
         <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I59">
         <v>13</v>
@@ -8645,10 +8650,10 @@
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" t="s">
         <v>182</v>
-      </c>
-      <c r="B60" t="s">
-        <v>183</v>
       </c>
       <c r="C60" t="s">
         <v>128</v>
@@ -8698,10 +8703,10 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>184</v>
+      </c>
+      <c r="B61" t="s">
         <v>185</v>
-      </c>
-      <c r="B61" t="s">
-        <v>186</v>
       </c>
       <c r="C61" t="s">
         <v>128</v>
@@ -8756,10 +8761,10 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" t="s">
         <v>185</v>
-      </c>
-      <c r="B62" t="s">
-        <v>186</v>
       </c>
       <c r="C62" t="s">
         <v>128</v>
@@ -8814,10 +8819,10 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s">
         <v>187</v>
-      </c>
-      <c r="B63" t="s">
-        <v>188</v>
       </c>
       <c r="C63" t="s">
         <v>128</v>
@@ -8872,10 +8877,10 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" t="s">
         <v>187</v>
-      </c>
-      <c r="B64" t="s">
-        <v>188</v>
       </c>
       <c r="C64" t="s">
         <v>128</v>
@@ -8930,10 +8935,10 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>188</v>
+      </c>
+      <c r="B65" t="s">
         <v>189</v>
-      </c>
-      <c r="B65" t="s">
-        <v>190</v>
       </c>
       <c r="C65" t="s">
         <v>128</v>
@@ -8988,10 +8993,10 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" t="s">
         <v>189</v>
-      </c>
-      <c r="B66" t="s">
-        <v>190</v>
       </c>
       <c r="C66" t="s">
         <v>128</v>
@@ -9046,13 +9051,13 @@
     </row>
     <row r="67" spans="1:22" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s">
         <v>191</v>
       </c>
-      <c r="B67" t="s">
-        <v>192</v>
-      </c>
       <c r="C67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D67">
         <v>0.03</v>
@@ -9099,13 +9104,13 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" t="s">
         <v>191</v>
       </c>
-      <c r="B68" t="s">
-        <v>192</v>
-      </c>
       <c r="C68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D68">
         <v>0.03</v>
@@ -9152,10 +9157,10 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" t="s">
         <v>193</v>
-      </c>
-      <c r="B69" t="s">
-        <v>194</v>
       </c>
       <c r="C69" t="s">
         <v>128</v>
@@ -9210,10 +9215,10 @@
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" t="s">
         <v>193</v>
-      </c>
-      <c r="B70" t="s">
-        <v>194</v>
       </c>
       <c r="C70" t="s">
         <v>128</v>
@@ -9268,10 +9273,10 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" t="s">
         <v>195</v>
-      </c>
-      <c r="B71" t="s">
-        <v>196</v>
       </c>
       <c r="C71" t="s">
         <v>122</v>
@@ -9321,10 +9326,10 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" t="s">
         <v>195</v>
-      </c>
-      <c r="B72" t="s">
-        <v>196</v>
       </c>
       <c r="C72" t="s">
         <v>122</v>
@@ -9374,10 +9379,10 @@
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" t="s">
         <v>197</v>
-      </c>
-      <c r="B73" t="s">
-        <v>198</v>
       </c>
       <c r="C73" t="s">
         <v>122</v>
@@ -9427,10 +9432,10 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74" t="s">
         <v>197</v>
-      </c>
-      <c r="B74" t="s">
-        <v>198</v>
       </c>
       <c r="C74" t="s">
         <v>122</v>
@@ -9468,7 +9473,7 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
         <v>162</v>
@@ -9526,7 +9531,7 @@
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B76" t="s">
         <v>162</v>
@@ -9584,16 +9589,16 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" t="s">
         <v>200</v>
-      </c>
-      <c r="B77" t="s">
-        <v>201</v>
       </c>
       <c r="C77" t="s">
         <v>122</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
@@ -9637,16 +9642,16 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" t="s">
         <v>200</v>
-      </c>
-      <c r="B78" t="s">
-        <v>201</v>
       </c>
       <c r="C78" t="s">
         <v>122</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E78" t="s">
         <v>29</v>
@@ -9690,7 +9695,7 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
         <v>162</v>
@@ -9748,7 +9753,7 @@
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B80" t="s">
         <v>162</v>
@@ -9806,10 +9811,10 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81" t="s">
         <v>204</v>
-      </c>
-      <c r="B81" t="s">
-        <v>205</v>
       </c>
       <c r="C81" t="s">
         <v>125</v>
@@ -9864,10 +9869,10 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>203</v>
+      </c>
+      <c r="B82" t="s">
         <v>204</v>
-      </c>
-      <c r="B82" t="s">
-        <v>205</v>
       </c>
       <c r="C82" t="s">
         <v>125</v>
@@ -9910,7 +9915,7 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.35">
@@ -9983,10 +9988,10 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>206</v>
+      </c>
+      <c r="B85" t="s">
         <v>207</v>
-      </c>
-      <c r="B85" t="s">
-        <v>208</v>
       </c>
       <c r="C85" t="s">
         <v>128</v>
@@ -10039,10 +10044,10 @@
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>206</v>
+      </c>
+      <c r="B86" t="s">
         <v>207</v>
-      </c>
-      <c r="B86" t="s">
-        <v>208</v>
       </c>
       <c r="C86" t="s">
         <v>128</v>
@@ -10095,10 +10100,10 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" t="s">
         <v>209</v>
-      </c>
-      <c r="B87" t="s">
-        <v>210</v>
       </c>
       <c r="C87" t="s">
         <v>128</v>
@@ -10151,10 +10156,10 @@
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>208</v>
+      </c>
+      <c r="B88" t="s">
         <v>209</v>
-      </c>
-      <c r="B88" t="s">
-        <v>210</v>
       </c>
       <c r="C88" t="s">
         <v>128</v>
@@ -10207,10 +10212,10 @@
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>210</v>
+      </c>
+      <c r="B89" t="s">
         <v>211</v>
-      </c>
-      <c r="B89" t="s">
-        <v>212</v>
       </c>
       <c r="C89" t="s">
         <v>128</v>
@@ -10263,10 +10268,10 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
+        <v>210</v>
+      </c>
+      <c r="B90" t="s">
         <v>211</v>
-      </c>
-      <c r="B90" t="s">
-        <v>212</v>
       </c>
       <c r="C90" t="s">
         <v>128</v>
@@ -10319,16 +10324,16 @@
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s">
-        <v>214</v>
+        <v>323</v>
       </c>
       <c r="C91" t="s">
         <v>128</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="E91" t="s">
         <v>29</v>
@@ -10367,16 +10372,16 @@
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s">
-        <v>214</v>
+        <v>323</v>
       </c>
       <c r="C92" t="s">
         <v>128</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="E92" t="s">
         <v>29</v>
@@ -10415,10 +10420,10 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="C93" t="s">
         <v>128</v>
@@ -10463,10 +10468,10 @@
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B94" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="C94" t="s">
         <v>128</v>
@@ -10511,10 +10516,10 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s">
         <v>128</v>
@@ -10569,10 +10574,10 @@
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B96" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s">
         <v>128</v>
@@ -10627,10 +10632,10 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C97" t="s">
         <v>128</v>
@@ -10683,10 +10688,10 @@
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B98" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C98" t="s">
         <v>128</v>
@@ -10739,10 +10744,10 @@
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C99" t="s">
         <v>128</v>
@@ -10795,10 +10800,10 @@
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C100" t="s">
         <v>128</v>
@@ -10854,7 +10859,7 @@
         <v>76</v>
       </c>
       <c r="B101" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C101" t="s">
         <v>128</v>
@@ -10910,7 +10915,7 @@
         <v>76</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C102" t="s">
         <v>128</v>
@@ -10963,7 +10968,7 @@
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.35">
@@ -11036,10 +11041,10 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C105" t="s">
         <v>128</v>
@@ -11094,10 +11099,10 @@
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C106" t="s">
         <v>128</v>
@@ -11112,7 +11117,7 @@
         <v>36</v>
       </c>
       <c r="G106" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H106" t="s">
         <v>119</v>
@@ -11152,10 +11157,10 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C107" t="s">
         <v>128</v>
@@ -11205,10 +11210,10 @@
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C108" t="s">
         <v>128</v>
@@ -11258,10 +11263,10 @@
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B109" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
         <v>128</v>
@@ -11311,10 +11316,10 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B110" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C110" t="s">
         <v>128</v>
@@ -11364,10 +11369,10 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B111" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C111" t="s">
         <v>128</v>
@@ -11422,10 +11427,10 @@
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B112" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C112" t="s">
         <v>128</v>
@@ -11480,10 +11485,10 @@
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B113" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C113" t="s">
         <v>128</v>
@@ -11538,10 +11543,10 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B114" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
@@ -11592,10 +11597,10 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B115" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C115" t="s">
         <v>128</v>
@@ -11646,10 +11651,10 @@
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C116" t="s">
         <v>128</v>
@@ -11700,7 +11705,7 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.35">
@@ -11773,10 +11778,10 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B119" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C119" t="s">
         <v>128</v>
@@ -11831,10 +11836,10 @@
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B120" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C120" t="s">
         <v>128</v>
@@ -11889,10 +11894,10 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C121" t="s">
         <v>128</v>
@@ -11947,10 +11952,10 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C122" t="s">
         <v>128</v>
@@ -12005,10 +12010,10 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B123" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C123" t="s">
         <v>128</v>
@@ -12058,10 +12063,10 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C124" t="s">
         <v>128</v>
@@ -12111,10 +12116,10 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B125" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C125" t="s">
         <v>122</v>
@@ -12164,10 +12169,10 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B126" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C126" t="s">
         <v>122</v>
@@ -12217,10 +12222,10 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B127" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C127" t="s">
         <v>128</v>
@@ -12275,10 +12280,10 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C128" t="s">
         <v>128</v>
@@ -12333,10 +12338,10 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C129" t="s">
         <v>128</v>
@@ -12391,10 +12396,10 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B130" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C130" t="s">
         <v>128</v>
@@ -12449,10 +12454,10 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C131" t="s">
         <v>122</v>
@@ -12507,10 +12512,10 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B132" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C132" t="s">
         <v>122</v>
@@ -12565,10 +12570,10 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B133" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C133" t="s">
         <v>128</v>
@@ -12613,10 +12618,10 @@
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B134" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C134" t="s">
         <v>128</v>
@@ -12661,10 +12666,10 @@
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B135" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C135" t="s">
         <v>128</v>
@@ -12719,10 +12724,10 @@
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B136" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C136" t="s">
         <v>128</v>
@@ -12777,10 +12782,10 @@
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B137" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
         <v>128</v>
@@ -12835,10 +12840,10 @@
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B138" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C138" t="s">
         <v>128</v>
@@ -12893,7 +12898,7 @@
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.35">
@@ -12966,16 +12971,16 @@
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B141" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C141" t="s">
         <v>128</v>
       </c>
       <c r="D141" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E141" t="s">
         <v>39</v>
@@ -13022,16 +13027,16 @@
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B142" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C142" t="s">
         <v>128</v>
       </c>
       <c r="D142" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E142" t="s">
         <v>39</v>
@@ -13078,10 +13083,10 @@
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B143" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C143" t="s">
         <v>128</v>
@@ -13131,10 +13136,10 @@
     </row>
     <row r="144" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C144" t="s">
         <v>128</v>
@@ -13184,10 +13189,10 @@
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B145" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C145" t="s">
         <v>128</v>
@@ -13242,10 +13247,10 @@
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B146" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C146" t="s">
         <v>128</v>
@@ -13300,10 +13305,10 @@
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B147" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C147" t="s">
         <v>128</v>
@@ -13358,10 +13363,10 @@
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B148" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C148" t="s">
         <v>128</v>
@@ -13408,10 +13413,10 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B149" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C149" t="s">
         <v>128</v>
@@ -13466,10 +13471,10 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B150" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C150" t="s">
         <v>128</v>
@@ -13524,10 +13529,10 @@
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B151" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C151" t="s">
         <v>128</v>
@@ -13582,10 +13587,10 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B152" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C152" t="s">
         <v>128</v>
@@ -13640,10 +13645,10 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B153" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C153" t="s">
         <v>125</v>
@@ -13696,10 +13701,10 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B154" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C154" t="s">
         <v>125</v>
@@ -13746,16 +13751,16 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B155" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C155" t="s">
         <v>116</v>
       </c>
       <c r="D155" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E155" t="s">
         <v>60</v>
@@ -13792,7 +13797,7 @@
       </c>
       <c r="P155" s="24"/>
       <c r="Q155" s="5" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="R155" s="24"/>
       <c r="S155" s="24"/>
@@ -13806,16 +13811,16 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B156" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C156" t="s">
         <v>116</v>
       </c>
       <c r="D156" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E156" t="s">
         <v>60</v>
@@ -13864,10 +13869,10 @@
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B157" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C157" t="s">
         <v>128</v>
@@ -13920,10 +13925,10 @@
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B158" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C158" t="s">
         <v>128</v>
@@ -13972,7 +13977,7 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.35">
@@ -14045,10 +14050,10 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B161" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C161" t="s">
         <v>128</v>
@@ -14101,10 +14106,10 @@
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C162" t="s">
         <v>128</v>
@@ -14157,10 +14162,10 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B163" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C163" t="s">
         <v>125</v>
@@ -14217,10 +14222,10 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C164" t="s">
         <v>125</v>
@@ -14273,10 +14278,10 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C165" t="s">
         <v>125</v>
@@ -14333,10 +14338,10 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C166" t="s">
         <v>125</v>
@@ -14393,10 +14398,10 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C167" t="s">
         <v>125</v>
@@ -14453,10 +14458,10 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B168" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C168" t="s">
         <v>125</v>
@@ -14511,10 +14516,10 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B169" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C169" t="s">
         <v>125</v>
@@ -14571,10 +14576,10 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B170" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C170" t="s">
         <v>125</v>
@@ -14627,10 +14632,10 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B171" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C171" t="s">
         <v>128</v>
@@ -14687,10 +14692,10 @@
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B172" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C172" t="s">
         <v>128</v>
@@ -14747,10 +14752,10 @@
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B173" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C173" t="s">
         <v>125</v>
@@ -14791,10 +14796,10 @@
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B174" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C174" t="s">
         <v>125</v>
@@ -14837,10 +14842,10 @@
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B175" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C175" t="s">
         <v>125</v>
@@ -14897,10 +14902,10 @@
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B176" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C176" t="s">
         <v>125</v>
@@ -14957,10 +14962,10 @@
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B177" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C177" t="s">
         <v>125</v>
@@ -15017,10 +15022,10 @@
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C178" t="s">
         <v>125</v>
@@ -15077,7 +15082,7 @@
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.35">
@@ -15150,10 +15155,10 @@
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B181" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C181" t="s">
         <v>125</v>
@@ -15197,10 +15202,10 @@
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B182" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C182" t="s">
         <v>125</v>
@@ -15240,10 +15245,10 @@
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B183" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C183" t="s">
         <v>116</v>
@@ -15298,10 +15303,10 @@
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B184" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C184" t="s">
         <v>116</v>
@@ -15356,16 +15361,16 @@
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B185" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C185" t="s">
         <v>128</v>
       </c>
       <c r="D185" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E185" t="s">
         <v>60</v>
@@ -15414,16 +15419,16 @@
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B186" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C186" t="s">
         <v>128</v>
       </c>
       <c r="D186" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E186" t="s">
         <v>60</v>
@@ -15466,10 +15471,10 @@
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B187" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C187" t="s">
         <v>128</v>
@@ -15524,10 +15529,10 @@
     </row>
     <row r="188" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B188" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C188" t="s">
         <v>128</v>
@@ -15576,10 +15581,10 @@
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B189" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C189" t="s">
         <v>128</v>
@@ -15629,10 +15634,10 @@
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B190" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C190" t="s">
         <v>128</v>
@@ -15673,16 +15678,16 @@
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B191" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C191" t="s">
         <v>128</v>
       </c>
       <c r="D191" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E191" t="s">
         <v>29</v>
@@ -15731,16 +15736,16 @@
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B192" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C192" t="s">
         <v>128</v>
       </c>
       <c r="D192" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E192" t="s">
         <v>29</v>
@@ -15787,16 +15792,16 @@
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B193" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C193" t="s">
         <v>128</v>
       </c>
       <c r="D193" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E193" t="s">
         <v>29</v>
@@ -15835,16 +15840,16 @@
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B194" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C194" t="s">
         <v>128</v>
       </c>
       <c r="D194" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E194" t="s">
         <v>29</v>
@@ -15881,10 +15886,10 @@
     </row>
     <row r="195" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B195" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C195" t="s">
         <v>125</v>
@@ -15929,10 +15934,10 @@
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B196" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C196" t="s">
         <v>125</v>
@@ -15973,10 +15978,10 @@
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B197" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C197" t="s">
         <v>125</v>
@@ -16023,10 +16028,10 @@
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B198" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C198" t="s">
         <v>125</v>
@@ -16067,10 +16072,10 @@
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B199" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C199" t="s">
         <v>125</v>
@@ -16125,10 +16130,10 @@
     </row>
     <row r="200" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B200" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C200" t="s">
         <v>125</v>
@@ -16200,12 +16205,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -16214,12 +16213,13 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -16357,16 +16357,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -16374,15 +16370,23 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16398,4 +16402,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2534" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05AC9672-95C1-417C-BF09-27EF830F2E30}"/>
+  <xr:revisionPtr revIDLastSave="2615" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F262AA-7DD4-4127-84E7-72D916DA78C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1344,7 +1344,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
@@ -1524,7 +1525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1560,7 +1561,6 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1575,6 +1575,8 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3240,7 +3242,9 @@
       <c r="R16" s="4">
         <v>0.81</v>
       </c>
-      <c r="S16" s="4"/>
+      <c r="S16" s="4">
+        <v>0.89</v>
+      </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
@@ -3632,7 +3636,9 @@
       <c r="R23" s="5">
         <v>0.13972119594175969</v>
       </c>
-      <c r="S23" s="5"/>
+      <c r="S23" s="5">
+        <v>0.13600000000000001</v>
+      </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
       <c r="V23" s="5"/>
@@ -3689,7 +3695,9 @@
       <c r="R24" s="5">
         <v>0.12649723977955013</v>
       </c>
-      <c r="S24" s="5"/>
+      <c r="S24" s="5">
+        <v>0.14699999999999999</v>
+      </c>
       <c r="T24" s="5"/>
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
@@ -3722,32 +3730,32 @@
       <c r="J25" t="s">
         <v>31</v>
       </c>
-      <c r="K25" s="37">
-        <v>0.254</v>
-      </c>
-      <c r="L25" s="37">
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="M25" s="37">
-        <v>0.96700000000000008</v>
-      </c>
-      <c r="N25" s="37">
-        <v>1.331</v>
-      </c>
-      <c r="O25" s="37">
-        <v>1.595</v>
+      <c r="K25" s="36">
+        <v>0.224</v>
+      </c>
+      <c r="L25" s="36">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="M25" s="36">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="N25" s="36">
+        <v>1.0409999999999999</v>
+      </c>
+      <c r="O25" s="36">
+        <v>1.155</v>
       </c>
       <c r="P25" s="7">
-        <v>2.1840000000000002</v>
+        <v>1.6040000000000001</v>
       </c>
       <c r="Q25" s="7">
-        <v>3.0979999999999999</v>
+        <v>2.4180000000000001</v>
       </c>
       <c r="R25" s="7">
-        <v>3.7</v>
+        <v>2.93</v>
       </c>
       <c r="S25" s="7">
-        <v>4.5439999999999996</v>
+        <v>3.7040000000000002</v>
       </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
@@ -3781,32 +3789,32 @@
       <c r="J26" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="35">
-        <v>0.28899999999999998</v>
-      </c>
-      <c r="L26" s="27">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="M26" s="35">
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="N26" s="35">
-        <v>1.5509999999999999</v>
-      </c>
-      <c r="O26" s="35">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="P26" s="7">
-        <v>2.5489999999999999</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>3.0990000000000002</v>
-      </c>
-      <c r="R26" s="7">
-        <v>3.895</v>
-      </c>
-      <c r="S26" s="7">
-        <v>5.0119999999999996</v>
+      <c r="K26" s="47">
+        <v>0.25983816666666698</v>
+      </c>
+      <c r="L26" s="47">
+        <v>0.38383816666666698</v>
+      </c>
+      <c r="M26" s="47">
+        <v>1.11283816666667</v>
+      </c>
+      <c r="N26" s="47">
+        <v>1.3223861666666701</v>
+      </c>
+      <c r="O26" s="47">
+        <v>1.65138616666667</v>
+      </c>
+      <c r="P26" s="48">
+        <v>2.1303861666666699</v>
+      </c>
+      <c r="Q26" s="48">
+        <v>2.6433861666666698</v>
+      </c>
+      <c r="R26" s="48">
+        <v>3.3972231666666701</v>
+      </c>
+      <c r="S26" s="48">
+        <v>4.5205241666666698</v>
       </c>
       <c r="T26" s="7"/>
       <c r="U26" s="7"/>
@@ -3864,7 +3872,9 @@
       <c r="R27" s="4">
         <v>0.23</v>
       </c>
-      <c r="S27" s="4"/>
+      <c r="S27" s="4">
+        <v>0.25</v>
+      </c>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
@@ -3921,7 +3931,9 @@
       <c r="R28" s="4">
         <v>0.3</v>
       </c>
-      <c r="S28" s="4"/>
+      <c r="S28" s="4">
+        <v>0.27</v>
+      </c>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
@@ -3984,7 +3996,9 @@
       <c r="R29" s="5">
         <v>0.33943248102419393</v>
       </c>
-      <c r="S29" s="5"/>
+      <c r="S29" s="5">
+        <v>0.33082830926903201</v>
+      </c>
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
@@ -4047,7 +4061,9 @@
       <c r="R30" s="5">
         <v>0.36691053201149237</v>
       </c>
-      <c r="S30" s="5"/>
+      <c r="S30" s="5">
+        <v>0.36899999999999999</v>
+      </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
       <c r="V30" s="5"/>
@@ -4245,7 +4261,9 @@
       <c r="R34" s="4">
         <v>0.94</v>
       </c>
-      <c r="S34" s="4"/>
+      <c r="S34" s="4">
+        <v>0.91</v>
+      </c>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
@@ -4407,8 +4425,12 @@
       <c r="Q37" s="4">
         <v>0.4</v>
       </c>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
+      <c r="R37" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0.4</v>
+      </c>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
@@ -4606,6 +4628,9 @@
       </c>
       <c r="R40">
         <v>51.9</v>
+      </c>
+      <c r="S40">
+        <v>55.8</v>
       </c>
       <c r="W40" t="s">
         <v>61</v>
@@ -4894,11 +4919,11 @@
       <c r="Q46" s="5">
         <v>0.39900000000000002</v>
       </c>
-      <c r="R46" s="4">
-        <v>0.35</v>
-      </c>
-      <c r="S46" s="4">
-        <v>0.35</v>
+      <c r="R46" s="5">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="S46" s="5">
+        <v>0.42299999999999999</v>
       </c>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
@@ -4956,7 +4981,9 @@
       <c r="R47" s="5" vm="22">
         <v>0.30756202137510114</v>
       </c>
-      <c r="S47" s="5"/>
+      <c r="S47" s="5">
+        <v>0.38100000000000001</v>
+      </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
@@ -5013,7 +5040,9 @@
       <c r="R48" s="5" vm="23">
         <v>0.28426058124592513</v>
       </c>
-      <c r="S48" s="5"/>
+      <c r="S48" s="5">
+        <v>0.378</v>
+      </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
@@ -5070,7 +5099,9 @@
       <c r="R49" s="5">
         <v>0.13500000000000001</v>
       </c>
-      <c r="S49" s="5"/>
+      <c r="S49" s="5">
+        <v>0.11600000000000001</v>
+      </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
@@ -5127,7 +5158,9 @@
       <c r="R50" s="5">
         <v>0.151</v>
       </c>
-      <c r="S50" s="5"/>
+      <c r="S50" s="5">
+        <v>0.17799999999999999</v>
+      </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
       <c r="V50" s="5"/>
@@ -5160,22 +5193,22 @@
       <c r="J51" t="s">
         <v>31</v>
       </c>
-      <c r="K51" s="38">
+      <c r="K51" s="37">
         <v>8.6903037999999988</v>
       </c>
-      <c r="L51" s="38">
+      <c r="L51" s="37">
         <v>14.05</v>
       </c>
-      <c r="M51" s="38">
+      <c r="M51" s="37">
         <v>24.179069699999999</v>
       </c>
-      <c r="N51" s="39">
+      <c r="N51" s="38">
         <v>33.551317699999998</v>
       </c>
-      <c r="O51" s="38">
+      <c r="O51" s="37">
         <v>41.442849800000005</v>
       </c>
-      <c r="P51" s="40">
+      <c r="P51" s="39">
         <v>60.823965100000009</v>
       </c>
       <c r="Q51">
@@ -5184,7 +5217,9 @@
       <c r="R51" s="8">
         <v>82.449704499999996</v>
       </c>
-      <c r="S51" s="7"/>
+      <c r="S51">
+        <v>97.4</v>
+      </c>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -5217,22 +5252,22 @@
       <c r="J52" t="s">
         <v>33</v>
       </c>
-      <c r="K52" s="41">
+      <c r="K52" s="40">
         <v>4.05</v>
       </c>
-      <c r="L52" s="41">
+      <c r="L52" s="40">
         <v>9.7989724000000002</v>
       </c>
-      <c r="M52" s="41">
+      <c r="M52" s="40">
         <v>25.313448100000002</v>
       </c>
-      <c r="N52" s="42">
+      <c r="N52" s="41">
         <v>31.452557499999998</v>
       </c>
-      <c r="O52" s="41">
+      <c r="O52" s="40">
         <v>41.128122899999994</v>
       </c>
-      <c r="P52" s="40">
+      <c r="P52" s="39">
         <v>55.164574999999999</v>
       </c>
       <c r="Q52" s="8">
@@ -5241,7 +5276,9 @@
       <c r="R52" s="8">
         <v>72.779408199999978</v>
       </c>
-      <c r="S52" s="7"/>
+      <c r="S52">
+        <v>91.2</v>
+      </c>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
@@ -5411,7 +5448,9 @@
       </c>
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
+      <c r="S57" s="4">
+        <v>0.91300000000000003</v>
+      </c>
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
@@ -6381,7 +6420,9 @@
       <c r="P16">
         <v>0.86</v>
       </c>
-      <c r="Q16" s="7"/>
+      <c r="Q16">
+        <v>0.8</v>
+      </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -6509,7 +6550,9 @@
       <c r="P18">
         <v>1.23</v>
       </c>
-      <c r="Q18" s="7"/>
+      <c r="Q18">
+        <v>1.3</v>
+      </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -6637,7 +6680,9 @@
       <c r="P20">
         <v>2.0099999999999998</v>
       </c>
-      <c r="Q20" s="7"/>
+      <c r="Q20">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -8214,7 +8259,9 @@
       <c r="P47" s="4">
         <v>0.95</v>
       </c>
-      <c r="Q47" s="4"/>
+      <c r="Q47" s="4">
+        <v>0.85</v>
+      </c>
       <c r="R47" s="4" t="s">
         <v>164</v>
       </c>
@@ -8280,7 +8327,9 @@
       <c r="P48" s="4">
         <v>0.71</v>
       </c>
-      <c r="Q48" s="4"/>
+      <c r="Q48" s="4">
+        <v>0.83</v>
+      </c>
       <c r="R48" s="4" t="s">
         <v>164</v>
       </c>
@@ -8414,7 +8463,9 @@
       <c r="P50">
         <v>25.31</v>
       </c>
-      <c r="Q50" s="8"/>
+      <c r="Q50">
+        <v>22.5</v>
+      </c>
       <c r="R50" s="8"/>
       <c r="S50" s="8"/>
       <c r="T50" s="8"/>
@@ -8932,7 +8983,9 @@
       <c r="P58" s="13">
         <v>0.29920000000000002</v>
       </c>
-      <c r="Q58" s="13"/>
+      <c r="Q58" s="13">
+        <v>0.27</v>
+      </c>
       <c r="R58" s="13"/>
       <c r="S58" s="13"/>
       <c r="T58" s="13"/>
@@ -9500,6 +9553,9 @@
       <c r="P67">
         <v>0.03</v>
       </c>
+      <c r="Q67">
+        <v>0.03</v>
+      </c>
       <c r="U67" t="s">
         <v>61</v>
       </c>
@@ -9538,10 +9594,10 @@
       <c r="J68" s="7">
         <v>0.04</v>
       </c>
-      <c r="K68" s="43">
+      <c r="K68" s="42">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="L68" s="43">
+      <c r="L68" s="42">
         <v>0</v>
       </c>
       <c r="M68" s="18">
@@ -9554,6 +9610,9 @@
         <v>0.01</v>
       </c>
       <c r="P68" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="Q68" s="7">
         <v>0.02</v>
       </c>
       <c r="U68" t="s">
@@ -10517,7 +10576,7 @@
       <c r="A85" t="s">
         <v>204</v>
       </c>
-      <c r="B85" s="44" t="s">
+      <c r="B85" s="43" t="s">
         <v>205</v>
       </c>
       <c r="C85" t="s">
@@ -10585,7 +10644,7 @@
       <c r="A86" t="s">
         <v>204</v>
       </c>
-      <c r="B86" s="44" t="s">
+      <c r="B86" s="43" t="s">
         <v>205</v>
       </c>
       <c r="C86" t="s">
@@ -10628,6 +10687,9 @@
         <v>75</v>
       </c>
       <c r="P86">
+        <v>75</v>
+      </c>
+      <c r="Q86">
         <v>75</v>
       </c>
       <c r="U86" t="s">
@@ -10753,6 +10815,9 @@
       </c>
       <c r="P88">
         <v>95</v>
+      </c>
+      <c r="Q88">
+        <v>90</v>
       </c>
       <c r="U88" t="s">
         <v>40</v>
@@ -11322,6 +11387,9 @@
       <c r="P98">
         <v>94</v>
       </c>
+      <c r="Q98">
+        <v>94</v>
+      </c>
       <c r="U98" t="s">
         <v>40</v>
       </c>
@@ -12605,7 +12673,9 @@
       <c r="P120" s="6">
         <v>0.53600000000000003</v>
       </c>
-      <c r="Q120" s="6"/>
+      <c r="Q120" s="6">
+        <v>0.53749999999999998</v>
+      </c>
       <c r="R120" s="6"/>
       <c r="S120" s="6"/>
       <c r="T120" s="6"/>
@@ -12733,7 +12803,9 @@
       <c r="P122" s="6">
         <v>0.40400000000000003</v>
       </c>
-      <c r="Q122" s="6"/>
+      <c r="Q122" s="6">
+        <v>0.40500000000000003</v>
+      </c>
       <c r="R122" s="6"/>
       <c r="S122" s="6"/>
       <c r="T122" s="6"/>
@@ -12861,6 +12933,9 @@
       <c r="P124">
         <v>0.6</v>
       </c>
+      <c r="Q124">
+        <v>0.9</v>
+      </c>
       <c r="U124" t="s">
         <v>61</v>
       </c>
@@ -12985,6 +13060,9 @@
       <c r="P126">
         <v>0.57499999999999996</v>
       </c>
+      <c r="Q126">
+        <v>0.75</v>
+      </c>
       <c r="U126" t="s">
         <v>61</v>
       </c>
@@ -13002,7 +13080,7 @@
       <c r="C127" t="s">
         <v>127</v>
       </c>
-      <c r="D127" s="46">
+      <c r="D127" s="45">
         <v>0.23599999999999999</v>
       </c>
       <c r="E127" t="s">
@@ -13070,7 +13148,7 @@
       <c r="C128" t="s">
         <v>127</v>
       </c>
-      <c r="D128" s="46">
+      <c r="D128" s="45">
         <v>0.23599999999999999</v>
       </c>
       <c r="E128" t="s">
@@ -13109,7 +13187,9 @@
       <c r="P128" s="12">
         <v>0.24</v>
       </c>
-      <c r="Q128" s="15"/>
+      <c r="Q128" s="12">
+        <v>0.24</v>
+      </c>
       <c r="R128" s="15"/>
       <c r="S128" s="15"/>
       <c r="T128" s="15"/>
@@ -13130,7 +13210,7 @@
       <c r="C129" t="s">
         <v>127</v>
       </c>
-      <c r="D129" s="46">
+      <c r="D129" s="45">
         <v>0.81599999999999995</v>
       </c>
       <c r="E129" t="s">
@@ -13198,7 +13278,7 @@
       <c r="C130" t="s">
         <v>127</v>
       </c>
-      <c r="D130" s="46">
+      <c r="D130" s="45">
         <v>0.81599999999999995</v>
       </c>
       <c r="E130" t="s">
@@ -13237,7 +13317,9 @@
       <c r="P130" s="15">
         <v>0.81200000000000006</v>
       </c>
-      <c r="Q130" s="15"/>
+      <c r="Q130" s="15">
+        <v>0.81200000000000006</v>
+      </c>
       <c r="R130" s="15"/>
       <c r="S130" s="15"/>
       <c r="T130" s="15"/>
@@ -13365,7 +13447,9 @@
       <c r="P132" s="12">
         <v>0.7</v>
       </c>
-      <c r="Q132" s="15"/>
+      <c r="Q132" s="15">
+        <v>0.70099999999999996</v>
+      </c>
       <c r="R132" s="15"/>
       <c r="S132" s="15"/>
       <c r="T132" s="15"/>
@@ -13527,7 +13611,9 @@
       <c r="P135" s="20">
         <v>49.6</v>
       </c>
-      <c r="Q135" s="20"/>
+      <c r="Q135" s="20">
+        <v>56.24</v>
+      </c>
       <c r="R135" s="20"/>
       <c r="S135" s="20"/>
       <c r="T135" s="20"/>
@@ -13572,7 +13658,7 @@
       <c r="K136" s="20">
         <v>17.7</v>
       </c>
-      <c r="L136" s="45">
+      <c r="L136" s="44">
         <v>23.77</v>
       </c>
       <c r="M136" s="20">
@@ -13587,7 +13673,9 @@
       <c r="P136" s="20">
         <v>48.8</v>
       </c>
-      <c r="Q136" s="20"/>
+      <c r="Q136" s="20">
+        <v>55.4</v>
+      </c>
       <c r="R136" s="20"/>
       <c r="S136" s="20"/>
       <c r="T136" s="20"/>
@@ -13608,7 +13696,7 @@
       <c r="C137" t="s">
         <v>127</v>
       </c>
-      <c r="D137" s="46">
+      <c r="D137" s="45">
         <v>0.52700000000000002</v>
       </c>
       <c r="E137" t="s">
@@ -13676,7 +13764,7 @@
       <c r="C138" t="s">
         <v>127</v>
       </c>
-      <c r="D138" s="46">
+      <c r="D138" s="45">
         <v>0.52700000000000002</v>
       </c>
       <c r="E138" t="s">
@@ -14809,40 +14897,40 @@
       <c r="H157" t="s">
         <v>116</v>
       </c>
-      <c r="I157" s="47">
+      <c r="I157" s="46">
         <v>40</v>
       </c>
-      <c r="J157" s="47">
+      <c r="J157" s="46">
         <v>40</v>
       </c>
-      <c r="K157" s="47">
+      <c r="K157" s="46">
         <v>40</v>
       </c>
-      <c r="L157" s="47">
+      <c r="L157" s="46">
         <v>40</v>
       </c>
-      <c r="M157" s="47">
+      <c r="M157" s="46">
         <v>40</v>
       </c>
-      <c r="N157" s="47">
+      <c r="N157" s="46">
         <v>40</v>
       </c>
-      <c r="O157" s="47">
+      <c r="O157" s="46">
         <v>40</v>
       </c>
-      <c r="P157" s="47">
+      <c r="P157" s="46">
         <v>40</v>
       </c>
-      <c r="Q157" s="47">
+      <c r="Q157" s="46">
         <v>40</v>
       </c>
-      <c r="R157" s="47">
+      <c r="R157" s="46">
         <v>40</v>
       </c>
-      <c r="S157" s="47">
+      <c r="S157" s="46">
         <v>40</v>
       </c>
-      <c r="T157" s="47">
+      <c r="T157" s="46">
         <v>40</v>
       </c>
       <c r="U157" t="s">
@@ -15225,9 +15313,9 @@
       <c r="Q164" s="12">
         <v>0.67</v>
       </c>
-      <c r="R164" s="36"/>
-      <c r="S164" s="36"/>
-      <c r="T164" s="36"/>
+      <c r="R164" s="35"/>
+      <c r="S164" s="35"/>
+      <c r="T164" s="35"/>
       <c r="U164" t="s">
         <v>40</v>
       </c>
@@ -15499,7 +15587,7 @@
       <c r="C169" t="s">
         <v>127</v>
       </c>
-      <c r="D169" s="46">
+      <c r="D169" s="45">
         <v>0.41299999999999998</v>
       </c>
       <c r="E169" t="s">
@@ -15567,7 +15655,7 @@
       <c r="C170" t="s">
         <v>127</v>
       </c>
-      <c r="D170" s="46">
+      <c r="D170" s="45">
         <v>0.41299999999999998</v>
       </c>
       <c r="E170" t="s">
@@ -15627,7 +15715,7 @@
       <c r="C171" t="s">
         <v>124</v>
       </c>
-      <c r="D171" s="46">
+      <c r="D171" s="45">
         <v>0.16500000000000001</v>
       </c>
       <c r="E171" t="s">
@@ -15673,7 +15761,7 @@
       <c r="C172" t="s">
         <v>124</v>
       </c>
-      <c r="D172" s="46">
+      <c r="D172" s="45">
         <v>0.16500000000000001</v>
       </c>
       <c r="E172" t="s">
@@ -16087,9 +16175,9 @@
       <c r="Q178" s="20">
         <v>9.1999999999999993</v>
       </c>
-      <c r="R178" s="45"/>
-      <c r="S178" s="45"/>
-      <c r="T178" s="45"/>
+      <c r="R178" s="44"/>
+      <c r="S178" s="44"/>
+      <c r="T178" s="44"/>
       <c r="U178" t="s">
         <v>40</v>
       </c>
@@ -17321,21 +17409,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17473,23 +17552,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2615" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F262AA-7DD4-4127-84E7-72D916DA78C4}"/>
+  <xr:revisionPtr revIDLastSave="2616" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7673D19-240A-406B-8BBC-E5CCD75926EB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13803,7 +13803,9 @@
       <c r="P138" s="15">
         <v>0.44400000000000001</v>
       </c>
-      <c r="Q138" s="15"/>
+      <c r="Q138" s="15">
+        <v>0.45400000000000001</v>
+      </c>
       <c r="R138" s="15"/>
       <c r="S138" s="15"/>
       <c r="T138" s="15"/>
@@ -17409,12 +17411,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17552,32 +17562,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2616" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7673D19-240A-406B-8BBC-E5CCD75926EB}"/>
+  <xr:revisionPtr revIDLastSave="2617" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E93DBB7-05EC-40D6-BA60-3B5A1B2996CE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3755,7 +3755,7 @@
         <v>2.93</v>
       </c>
       <c r="S25" s="7">
-        <v>3.7040000000000002</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
@@ -17411,20 +17411,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17562,24 +17554,32 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2617" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E93DBB7-05EC-40D6-BA60-3B5A1B2996CE}"/>
+  <xr:revisionPtr revIDLastSave="2619" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{691ADE7F-FF2F-457E-8C38-05CBD712C28E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4262,7 +4262,7 @@
         <v>0.94</v>
       </c>
       <c r="S34" s="4">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -11514,6 +11514,9 @@
       <c r="P100">
         <v>88</v>
       </c>
+      <c r="Q100">
+        <v>86</v>
+      </c>
       <c r="U100" t="s">
         <v>40</v>
       </c>
@@ -17411,12 +17414,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17554,32 +17571,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -4958,16 +4958,8 @@
         </is>
       </c>
       <c r="S51" s="50" t="n"/>
-      <c r="T51" s="50" t="inlineStr">
-        <is>
-          <t>QTR</t>
-        </is>
-      </c>
-      <c r="U51" s="50" t="inlineStr">
-        <is>
-          <t>QTR</t>
-        </is>
-      </c>
+      <c r="T51" s="50" t="n"/>
+      <c r="U51" s="50" t="n"/>
       <c r="V51" s="50" t="n"/>
       <c r="W51" t="inlineStr">
         <is>
@@ -5062,16 +5054,8 @@
           <t>QTR</t>
         </is>
       </c>
-      <c r="T52" s="7" t="inlineStr">
-        <is>
-          <t>QTR</t>
-        </is>
-      </c>
-      <c r="U52" s="7" t="inlineStr">
-        <is>
-          <t>QTR</t>
-        </is>
-      </c>
+      <c r="T52" s="7" t="n"/>
+      <c r="U52" s="7" t="n"/>
       <c r="V52" s="7" t="n"/>
       <c r="W52" t="inlineStr">
         <is>

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPR Masterfile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DMB Masterfile" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPR Masterfile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMB Masterfile" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -1708,6 +1708,9 @@
       <c r="R9" t="n">
         <v>1</v>
       </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Whole Number</t>
@@ -4957,7 +4960,11 @@
           <t>QTR</t>
         </is>
       </c>
-      <c r="S51" s="50" t="n"/>
+      <c r="S51" s="50" t="inlineStr">
+        <is>
+          <t>QTR</t>
+        </is>
+      </c>
       <c r="T51" s="50" t="n"/>
       <c r="U51" s="50" t="n"/>
       <c r="V51" s="50" t="n"/>
@@ -5042,7 +5049,7 @@
         </is>
       </c>
       <c r="P52" s="39" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
@@ -5050,6 +5057,11 @@
         </is>
       </c>
       <c r="R52" s="8" t="inlineStr">
+        <is>
+          <t>QTR</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
@@ -5473,7 +5485,11 @@
         </is>
       </c>
       <c r="R59" s="12" t="n"/>
-      <c r="S59" s="12" t="n"/>
+      <c r="S59" s="12" t="inlineStr">
+        <is>
+          <t>HY</t>
+        </is>
+      </c>
       <c r="T59" s="12" t="n"/>
       <c r="U59" s="12" t="n"/>
       <c r="V59" s="12" t="n"/>
@@ -9053,17 +9069,17 @@
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -9147,17 +9163,17 @@
       </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -11281,26 +11297,6 @@
       <c r="J74" t="n">
         <v>7</v>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
@@ -11805,10 +11801,8 @@
       <c r="P80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" s="12" t="inlineStr">
-        <is>
-          <t>90%%</t>
-        </is>
+      <c r="Q80" s="12" t="n">
+        <v>0.9</v>
       </c>
       <c r="R80" s="12" t="n"/>
       <c r="S80" s="12" t="n"/>
@@ -11949,36 +11943,12 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I82" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M82" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I82" s="34" t="n"/>
+      <c r="J82" s="34" t="n"/>
+      <c r="K82" s="34" t="n"/>
+      <c r="L82" s="34" t="n"/>
+      <c r="M82" s="34" t="n"/>
+      <c r="N82" s="34" t="n"/>
       <c r="O82" s="20" t="n">
         <v>1</v>
       </c>
@@ -14328,10 +14298,8 @@
       <c r="P112" s="2" t="n">
         <v>0.345</v>
       </c>
-      <c r="Q112" s="3" t="inlineStr">
-        <is>
-          <t>35.2%</t>
-        </is>
+      <c r="Q112" s="3" t="n">
+        <v>0.352</v>
       </c>
       <c r="R112" s="2" t="n"/>
       <c r="S112" s="2" t="n"/>

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPR Masterfile" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMB Masterfile" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -23,7 +23,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="0.000_);\(0.000\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -65,23 +65,9 @@
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <b val="1"/>
       <color theme="0"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -204,7 +190,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -219,9 +205,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,23 +215,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -254,9 +233,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -685,28 +662,28 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Drive_growth_through_CommercialExcellence" displayName="Drive_growth_through_CommercialExcellence" ref="A42:W52" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A42:W52"/>
   <tableColumns count="23">
-    <tableColumn id="1" name="Core KPI's"/>
-    <tableColumn id="2" name="Metric Owner"/>
-    <tableColumn id="3" name="KPI  Definition"/>
-    <tableColumn id="4" name="AOP 2026"/>
-    <tableColumn id="5" name="Column1"/>
-    <tableColumn id="6" name="Column2"/>
-    <tableColumn id="7" name="Metric nature"/>
-    <tableColumn id="8" name="Units"/>
-    <tableColumn id="9" name="Frequency"/>
-    <tableColumn id="10" name="Target/_x000a_Actual"/>
-    <tableColumn id="11" name="Jan"/>
-    <tableColumn id="12" name="Feb"/>
-    <tableColumn id="13" name="Mar"/>
-    <tableColumn id="14" name="Apr"/>
-    <tableColumn id="15" name="May"/>
-    <tableColumn id="16" name="Jun"/>
-    <tableColumn id="17" name="Jul"/>
-    <tableColumn id="18" name="Aug"/>
-    <tableColumn id="19" name="Sep"/>
-    <tableColumn id="20" name="Oct"/>
-    <tableColumn id="21" name="Nov"/>
-    <tableColumn id="22" name="Dec"/>
+    <tableColumn id="1" name="I2M Value Creation"/>
+    <tableColumn id="2" name="Shivaraj G"/>
+    <tableColumn id="3" name="Development progress (per year, per quarter, %) X Incremental IGM"/>
+    <tableColumn id="4" name="TBD"/>
+    <tableColumn id="5" name="TBD2"/>
+    <tableColumn id="6" name="TBD3"/>
+    <tableColumn id="7" name="Higher the better"/>
+    <tableColumn id="8" name="Mn"/>
+    <tableColumn id="9" name="Monthly"/>
+    <tableColumn id="10" name="A"/>
+    <tableColumn id="11" name="9"/>
+    <tableColumn id="12" name="17.3"/>
+    <tableColumn id="13" name="24.6"/>
+    <tableColumn id="14" name="26.3"/>
+    <tableColumn id="15" name="31"/>
+    <tableColumn id="16" name="37"/>
+    <tableColumn id="17" name="49.7"/>
+    <tableColumn id="18" name="51.9"/>
+    <tableColumn id="19" name="55.8"/>
+    <tableColumn id="20" name="Column4"/>
+    <tableColumn id="21" name="Column5"/>
+    <tableColumn id="22" name="Column6"/>
     <tableColumn id="23" name="Data Type"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1192,26 +1169,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="40" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col hidden="1" width="17.85546875" customWidth="1" min="2" max="2"/>
-    <col hidden="1" width="55.28515625" customWidth="1" min="3" max="3"/>
-    <col hidden="1" width="8.7109375" customWidth="1" min="4" max="4"/>
-    <col hidden="1" width="10.7109375" customWidth="1" min="5" max="6"/>
-    <col hidden="1" width="15.5703125" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="8.7109375" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="12.7109375" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="15.140625" customWidth="1" min="10" max="10"/>
-    <col width="8.7109375" customWidth="1" min="11" max="13"/>
-    <col width="8.140625" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="17.81640625" customWidth="1" min="2" max="2"/>
+    <col hidden="1" width="55.26953125" customWidth="1" min="3" max="3"/>
+    <col hidden="1" width="8.7265625" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="10.7265625" customWidth="1" min="5" max="6"/>
+    <col hidden="1" width="15.54296875" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="8.7265625" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="12.7265625" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="15.1796875" customWidth="1" min="10" max="10"/>
+    <col width="8.7265625" customWidth="1" min="11" max="13"/>
+    <col width="8.1796875" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="11.42578125" bestFit="1" customWidth="1" min="16" max="17"/>
-    <col width="14.42578125" customWidth="1" min="23" max="23"/>
+    <col width="11.453125" bestFit="1" customWidth="1" min="16" max="17"/>
+    <col width="14.453125" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.95" customHeight="1">
-      <c r="A1" s="49" t="inlineStr">
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>Strategic Imperatives</t>
         </is>
@@ -1382,40 +1359,40 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K5" s="33" t="n">
+      <c r="K5" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="L5" s="33" t="n">
+      <c r="L5" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="M5" s="33" t="n">
+      <c r="M5" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="N5" s="33" t="n">
+      <c r="N5" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O5" s="33" t="n">
+      <c r="O5" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P5" s="33" t="n">
+      <c r="P5" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="Q5" s="33" t="n">
+      <c r="Q5" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="R5" s="33" t="n">
+      <c r="R5" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="S5" s="33" t="n">
+      <c r="S5" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="T5" s="33" t="n">
+      <c r="T5" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="U5" s="33" t="n">
+      <c r="U5" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="V5" s="33" t="n">
+      <c r="V5" s="29" t="n">
         <v>0.05</v>
       </c>
       <c r="W5" t="inlineStr">
@@ -1463,36 +1440,36 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="41" t="n">
         <v>0.038</v>
       </c>
-      <c r="L6" s="50" t="n">
+      <c r="L6" s="41" t="n">
         <v>0.038</v>
       </c>
-      <c r="M6" s="50" t="n">
+      <c r="M6" s="41" t="n">
         <v>0.028</v>
       </c>
-      <c r="N6" s="50" t="n">
+      <c r="N6" s="41" t="n">
         <v>0.026</v>
       </c>
-      <c r="O6" s="50" t="n">
+      <c r="O6" s="41" t="n">
         <v>0.026</v>
       </c>
-      <c r="P6" s="50" t="n">
+      <c r="P6" s="41" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q6" s="50" t="n">
+      <c r="Q6" s="41" t="n">
         <v>0.031</v>
       </c>
-      <c r="R6" s="50" t="n">
+      <c r="R6" s="41" t="n">
         <v>0.035</v>
       </c>
-      <c r="S6" s="50" t="n">
+      <c r="S6" s="41" t="n">
         <v>0.035</v>
       </c>
-      <c r="T6" s="50" t="n"/>
-      <c r="U6" s="50" t="n"/>
-      <c r="V6" s="50" t="n"/>
+      <c r="T6" s="41" t="n"/>
+      <c r="U6" s="41" t="n"/>
+      <c r="V6" s="41" t="n"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Percentage</t>
@@ -1538,29 +1515,33 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K7" s="33" t="n">
+      <c r="K7" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="L7" s="33" t="n">
+      <c r="L7" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="M7" s="33" t="n">
+      <c r="M7" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="N7" s="33" t="n">
+      <c r="N7" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="O7" s="33" t="n">
+      <c r="O7" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="P7" s="33" t="n">
+      <c r="P7" s="29" t="n">
         <v>0.9</v>
       </c>
       <c r="Q7" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
+      <c r="R7" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>0.9</v>
+      </c>
       <c r="T7" s="12" t="n"/>
       <c r="U7" s="12" t="n"/>
       <c r="V7" s="12" t="n"/>
@@ -1609,19 +1590,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K8" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="50" t="n">
+      <c r="L8" s="41" t="n">
         <v>0.75</v>
       </c>
-      <c r="M8" s="50" t="n">
+      <c r="M8" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="N8" s="50" t="n">
+      <c r="N8" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="50" t="n">
+      <c r="O8" s="41" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="13" t="n">
@@ -1684,19 +1665,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K9" s="25" t="n">
+      <c r="K9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="25" t="n">
+      <c r="L9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="25" t="n">
+      <c r="M9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="25" t="n">
+      <c r="N9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="25" t="n">
+      <c r="O9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
@@ -1756,19 +1737,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K10" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="27" t="n">
+      <c r="O10" s="25" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
@@ -1835,19 +1816,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K11" s="51" t="n">
+      <c r="K11" s="42" t="n">
         <v>0.0191</v>
       </c>
-      <c r="L11" s="51" t="n">
+      <c r="L11" s="42" t="n">
         <v>0.0407</v>
       </c>
-      <c r="M11" s="51" t="n">
+      <c r="M11" s="42" t="n">
         <v>0.0462</v>
       </c>
-      <c r="N11" s="51" t="n">
+      <c r="N11" s="42" t="n">
         <v>0.0386</v>
       </c>
-      <c r="O11" s="51" t="n">
+      <c r="O11" s="42" t="n">
         <v>0.0353</v>
       </c>
       <c r="P11" s="15" t="n">
@@ -1923,22 +1904,22 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K12" s="51" t="n">
+      <c r="K12" s="42" t="n">
         <v>0.0092</v>
       </c>
-      <c r="L12" s="51" t="n">
+      <c r="L12" s="42" t="n">
         <v>0.0158</v>
       </c>
-      <c r="M12" s="51" t="n">
+      <c r="M12" s="42" t="n">
         <v>0.0176</v>
       </c>
-      <c r="N12" s="51" t="n">
+      <c r="N12" s="42" t="n">
         <v>0.0158</v>
       </c>
-      <c r="O12" s="51" t="n">
+      <c r="O12" s="42" t="n">
         <v>0.0086</v>
       </c>
-      <c r="P12" s="51" t="n">
+      <c r="P12" s="42" t="n">
         <v>0.0127</v>
       </c>
       <c r="Q12" s="15" t="n">
@@ -2123,19 +2104,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K15" s="33" t="n">
+      <c r="K15" s="29" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="L15" s="33" t="n">
+      <c r="L15" s="29" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M15" s="33" t="n">
+      <c r="M15" s="29" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N15" s="33" t="n">
+      <c r="N15" s="29" t="n">
         <v>0.72</v>
       </c>
-      <c r="O15" s="33" t="n">
+      <c r="O15" s="29" t="n">
         <v>0.72</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -2205,19 +2186,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K16" s="33" t="n">
+      <c r="K16" s="29" t="n">
         <v>0.83</v>
       </c>
-      <c r="L16" s="33" t="n">
+      <c r="L16" s="29" t="n">
         <v>0.82</v>
       </c>
-      <c r="M16" s="33" t="n">
+      <c r="M16" s="29" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="N16" s="33" t="n">
+      <c r="N16" s="29" t="n">
         <v>0.6</v>
       </c>
-      <c r="O16" s="33" t="n">
+      <c r="O16" s="29" t="n">
         <v>0.87</v>
       </c>
       <c r="P16" s="12" t="n">
@@ -2281,19 +2262,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K17" s="50" t="n">
+      <c r="K17" s="41" t="n">
         <v>0.5425</v>
       </c>
-      <c r="L17" s="50" t="n">
+      <c r="L17" s="41" t="n">
         <v>0.5439999999999999</v>
       </c>
-      <c r="M17" s="50" t="n">
+      <c r="M17" s="41" t="n">
         <v>0.5454999999999999</v>
       </c>
-      <c r="N17" s="50" t="n">
+      <c r="N17" s="41" t="n">
         <v>0.5469999999999998</v>
       </c>
-      <c r="O17" s="50" t="n">
+      <c r="O17" s="41" t="n">
         <v>0.5484999999999998</v>
       </c>
       <c r="P17" s="13" t="n">
@@ -2357,19 +2338,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="41" t="n">
         <v>0.5178</v>
       </c>
-      <c r="L18" s="50" t="n">
+      <c r="L18" s="41" t="n">
         <v>0.541</v>
       </c>
-      <c r="M18" s="50" t="n">
+      <c r="M18" s="41" t="n">
         <v>0.541</v>
       </c>
-      <c r="N18" s="50" t="n">
+      <c r="N18" s="41" t="n">
         <v>0.5397</v>
       </c>
-      <c r="O18" s="50" t="n">
+      <c r="O18" s="41" t="n">
         <v>0.541</v>
       </c>
       <c r="P18" s="13" t="n">
@@ -2443,19 +2424,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K19" s="51" t="n">
+      <c r="K19" s="42" t="n">
         <v>0.732</v>
       </c>
-      <c r="L19" s="51" t="n">
+      <c r="L19" s="42" t="n">
         <v>0.7274999999999999</v>
       </c>
-      <c r="M19" s="51" t="n">
+      <c r="M19" s="42" t="n">
         <v>0.7287499999999999</v>
       </c>
-      <c r="N19" s="51" t="n">
+      <c r="N19" s="42" t="n">
         <v>0.7299999999999999</v>
       </c>
-      <c r="O19" s="51" t="n">
+      <c r="O19" s="42" t="n">
         <v>0.7312499999999998</v>
       </c>
       <c r="P19" s="15" t="n">
@@ -2535,19 +2516,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K20" s="51" t="n">
+      <c r="K20" s="42" t="n">
         <v>0.6929999999999999</v>
       </c>
-      <c r="L20" s="51" t="n">
+      <c r="L20" s="42" t="n">
         <v>0.711</v>
       </c>
-      <c r="M20" s="51" t="n">
+      <c r="M20" s="42" t="n">
         <v>0.725</v>
       </c>
-      <c r="N20" s="51" t="n">
+      <c r="N20" s="42" t="n">
         <v>0.723</v>
       </c>
-      <c r="O20" s="51" t="n">
+      <c r="O20" s="42" t="n">
         <v>0.736</v>
       </c>
       <c r="P20" s="15" t="n">
@@ -2738,19 +2719,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K23" s="50" t="n">
+      <c r="K23" s="41" t="n">
         <v>0.1177401469338462</v>
       </c>
-      <c r="L23" s="50" t="n">
+      <c r="L23" s="41" t="n">
         <v>0.07682363314050382</v>
       </c>
-      <c r="M23" s="50" t="n">
+      <c r="M23" s="41" t="n">
         <v>0.074</v>
       </c>
-      <c r="N23" s="50" t="n">
+      <c r="N23" s="41" t="n">
         <v>0.09996246377660442</v>
       </c>
-      <c r="O23" s="50" t="n">
+      <c r="O23" s="41" t="n">
         <v>0.1038498729590533</v>
       </c>
       <c r="P23" s="13" t="n">
@@ -2815,19 +2796,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K24" s="50" t="n">
+      <c r="K24" s="41" t="n">
         <v>-0.04253311543933095</v>
       </c>
-      <c r="L24" s="50" t="n">
+      <c r="L24" s="41" t="n">
         <v>0.07801317462250906</v>
       </c>
-      <c r="M24" s="50" t="n">
+      <c r="M24" s="41" t="n">
         <v>0.147</v>
       </c>
-      <c r="N24" s="50" t="n">
+      <c r="N24" s="41" t="n">
         <v>0.136783223203627</v>
       </c>
-      <c r="O24" s="50" t="n">
+      <c r="O24" s="41" t="n">
         <v>0.1455830390815941</v>
       </c>
       <c r="P24" s="13" t="n">
@@ -2892,36 +2873,36 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K25" s="52" t="n">
+      <c r="K25" s="43" t="n">
         <v>0.224</v>
       </c>
-      <c r="L25" s="52" t="n">
+      <c r="L25" s="43" t="n">
         <v>0.358</v>
       </c>
-      <c r="M25" s="52" t="n">
+      <c r="M25" s="43" t="n">
         <v>0.797</v>
       </c>
-      <c r="N25" s="52" t="n">
+      <c r="N25" s="43" t="n">
         <v>1.041</v>
       </c>
-      <c r="O25" s="52" t="n">
+      <c r="O25" s="43" t="n">
         <v>1.155</v>
       </c>
-      <c r="P25" s="52" t="n">
+      <c r="P25" s="43" t="n">
         <v>1.604</v>
       </c>
-      <c r="Q25" s="52" t="n">
+      <c r="Q25" s="43" t="n">
         <v>2.418</v>
       </c>
-      <c r="R25" s="52" t="n">
+      <c r="R25" s="43" t="n">
         <v>2.93</v>
       </c>
-      <c r="S25" s="52" t="n">
+      <c r="S25" s="43" t="n">
         <v>4.27</v>
       </c>
-      <c r="T25" s="52" t="n"/>
-      <c r="U25" s="52" t="n"/>
-      <c r="V25" s="52" t="n"/>
+      <c r="T25" s="43" t="n"/>
+      <c r="U25" s="43" t="n"/>
+      <c r="V25" s="43" t="n"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -2969,36 +2950,36 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K26" s="52" t="n">
+      <c r="K26" s="43" t="n">
         <v>0.2598381666666667</v>
       </c>
-      <c r="L26" s="52" t="n">
+      <c r="L26" s="43" t="n">
         <v>0.3838381666666667</v>
       </c>
-      <c r="M26" s="52" t="n">
+      <c r="M26" s="43" t="n">
         <v>1.112838166666667</v>
       </c>
-      <c r="N26" s="52" t="n">
+      <c r="N26" s="43" t="n">
         <v>1.322386166666667</v>
       </c>
-      <c r="O26" s="52" t="n">
+      <c r="O26" s="43" t="n">
         <v>1.651386166666667</v>
       </c>
-      <c r="P26" s="52" t="n">
+      <c r="P26" s="43" t="n">
         <v>2.130386166666667</v>
       </c>
-      <c r="Q26" s="52" t="n">
+      <c r="Q26" s="43" t="n">
         <v>2.643386166666667</v>
       </c>
-      <c r="R26" s="52" t="n">
+      <c r="R26" s="43" t="n">
         <v>3.397223166666667</v>
       </c>
-      <c r="S26" s="52" t="n">
+      <c r="S26" s="43" t="n">
         <v>4.520524166666666</v>
       </c>
-      <c r="T26" s="52" t="n"/>
-      <c r="U26" s="52" t="n"/>
-      <c r="V26" s="52" t="n"/>
+      <c r="T26" s="43" t="n"/>
+      <c r="U26" s="43" t="n"/>
+      <c r="V26" s="43" t="n"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -3046,19 +3027,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K27" s="33" t="n">
+      <c r="K27" s="29" t="n">
         <v>0.284</v>
       </c>
-      <c r="L27" s="33" t="n">
+      <c r="L27" s="29" t="n">
         <v>0.2826</v>
       </c>
-      <c r="M27" s="33" t="n">
+      <c r="M27" s="29" t="n">
         <v>0.29</v>
       </c>
-      <c r="N27" s="33" t="n">
+      <c r="N27" s="29" t="n">
         <v>0.29</v>
       </c>
-      <c r="O27" s="33" t="n">
+      <c r="O27" s="29" t="n">
         <v>0.27</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -3123,19 +3104,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K28" s="33" t="n">
+      <c r="K28" s="29" t="n">
         <v>0.274</v>
       </c>
-      <c r="L28" s="33" t="n">
+      <c r="L28" s="29" t="n">
         <v>0.299</v>
       </c>
-      <c r="M28" s="33" t="n">
+      <c r="M28" s="29" t="n">
         <v>0.29</v>
       </c>
-      <c r="N28" s="33" t="n">
+      <c r="N28" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="O28" s="33" t="n">
+      <c r="O28" s="29" t="n">
         <v>0.31</v>
       </c>
       <c r="P28" s="12" t="n">
@@ -3208,19 +3189,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="41" t="n">
         <v>0.3470007298587861</v>
       </c>
-      <c r="L29" s="50" t="n">
+      <c r="L29" s="41" t="n">
         <v>0.3285452766190238</v>
       </c>
-      <c r="M29" s="50" t="n">
+      <c r="M29" s="41" t="n">
         <v>0.3019165275158768</v>
       </c>
-      <c r="N29" s="50" t="n">
+      <c r="N29" s="41" t="n">
         <v>0.3223317588974893</v>
       </c>
-      <c r="O29" s="50" t="n">
+      <c r="O29" s="41" t="n">
         <v>0.3273296571292933</v>
       </c>
       <c r="P29" s="13" t="n">
@@ -3293,19 +3274,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K30" s="41" t="n">
         <v>0.365917700116868</v>
       </c>
-      <c r="L30" s="50" t="n">
+      <c r="L30" s="41" t="n">
         <v>0.4334651430230574</v>
       </c>
-      <c r="M30" s="50" t="n">
+      <c r="M30" s="41" t="n">
         <v>0.4131984444971177</v>
       </c>
-      <c r="N30" s="50" t="n">
+      <c r="N30" s="41" t="n">
         <v>0.4119500597432678</v>
       </c>
-      <c r="O30" s="50" t="n">
+      <c r="O30" s="41" t="n">
         <v>0.4074770416160732</v>
       </c>
       <c r="P30" s="13" t="n">
@@ -3493,19 +3474,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K33" s="33" t="n">
+      <c r="K33" s="29" t="n">
         <v>0.34</v>
       </c>
-      <c r="L33" s="33" t="n">
+      <c r="L33" s="29" t="n">
         <v>0.34</v>
       </c>
-      <c r="M33" s="33" t="n">
+      <c r="M33" s="29" t="n">
         <v>0.34</v>
       </c>
-      <c r="N33" s="33" t="n">
+      <c r="N33" s="29" t="n">
         <v>0.34</v>
       </c>
-      <c r="O33" s="33" t="n">
+      <c r="O33" s="29" t="n">
         <v>0.34</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -3568,19 +3549,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K34" s="33" t="n">
+      <c r="K34" s="29" t="n">
         <v>0.318</v>
       </c>
-      <c r="L34" s="33" t="n">
+      <c r="L34" s="29" t="n">
         <v>0.358</v>
       </c>
-      <c r="M34" s="33" t="n">
+      <c r="M34" s="29" t="n">
         <v>0.415</v>
       </c>
-      <c r="N34" s="33" t="n">
+      <c r="N34" s="29" t="n">
         <v>0.405</v>
       </c>
-      <c r="O34" s="33" t="n">
+      <c r="O34" s="29" t="n">
         <v>0.371</v>
       </c>
       <c r="P34" s="12" t="n">
@@ -3643,19 +3624,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K35" s="33" t="n">
+      <c r="K35" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="L35" s="33" t="n">
+      <c r="L35" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="M35" s="33" t="n">
+      <c r="M35" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="N35" s="33" t="n">
+      <c r="N35" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="O35" s="33" t="n">
+      <c r="O35" s="29" t="n">
         <v>0.9</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3724,19 +3705,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K36" s="33" t="n">
+      <c r="K36" s="29" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="L36" s="33" t="n">
+      <c r="L36" s="29" t="n">
         <v>0.78</v>
       </c>
-      <c r="M36" s="33" t="n">
+      <c r="M36" s="29" t="n">
         <v>0.8</v>
       </c>
-      <c r="N36" s="33" t="n">
+      <c r="N36" s="29" t="n">
         <v>0.82</v>
       </c>
-      <c r="O36" s="33" t="n">
+      <c r="O36" s="29" t="n">
         <v>0.795</v>
       </c>
       <c r="P36" s="12" t="n">
@@ -3811,13 +3792,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K37" s="50" t="n"/>
-      <c r="L37" s="50" t="n"/>
-      <c r="M37" s="50" t="n">
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="41" t="n"/>
+      <c r="M37" s="41" t="n">
         <v>0.05</v>
       </c>
-      <c r="N37" s="50" t="n"/>
-      <c r="O37" s="50" t="n"/>
+      <c r="N37" s="41" t="n"/>
+      <c r="O37" s="41" t="n"/>
       <c r="P37" s="13" t="n">
         <v>0.055</v>
       </c>
@@ -3884,25 +3865,25 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K38" s="29" t="inlineStr">
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="L38" s="29" t="inlineStr">
+      <c r="L38" s="26" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="M38" s="29" t="n">
+      <c r="M38" s="26" t="n">
         <v>0.042</v>
       </c>
-      <c r="N38" s="29" t="inlineStr">
+      <c r="N38" s="26" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="O38" s="29" t="inlineStr">
+      <c r="O38" s="26" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
@@ -3989,36 +3970,36 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K39" s="50" t="n">
+      <c r="K39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="L39" s="50" t="n">
+      <c r="L39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="M39" s="50" t="n">
+      <c r="M39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="N39" s="50" t="n">
+      <c r="N39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="O39" s="50" t="n">
+      <c r="O39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="P39" s="50" t="n">
+      <c r="P39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q39" s="50" t="n">
+      <c r="Q39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="R39" s="50" t="n">
+      <c r="R39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="S39" s="50" t="n">
+      <c r="S39" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="T39" s="50" t="n"/>
-      <c r="U39" s="50" t="n"/>
-      <c r="V39" s="50" t="n"/>
+      <c r="T39" s="41" t="n"/>
+      <c r="U39" s="41" t="n"/>
+      <c r="V39" s="41" t="n"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -4076,36 +4057,36 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K40" s="50" t="n">
+      <c r="K40" s="41" t="n">
         <v>0.66</v>
       </c>
-      <c r="L40" s="50" t="n">
+      <c r="L40" s="41" t="n">
         <v>0.34</v>
       </c>
-      <c r="M40" s="50" t="n">
+      <c r="M40" s="41" t="n">
         <v>0.41</v>
       </c>
-      <c r="N40" s="50" t="n">
+      <c r="N40" s="41" t="n">
         <v>0.39</v>
       </c>
-      <c r="O40" s="50" t="n">
+      <c r="O40" s="41" t="n">
         <v>0.408</v>
       </c>
-      <c r="P40" s="50" t="n">
+      <c r="P40" s="41" t="n">
         <v>0.43</v>
       </c>
-      <c r="Q40" s="50" t="n">
+      <c r="Q40" s="41" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="R40" s="50" t="n">
+      <c r="R40" s="41" t="n">
         <v>0.39</v>
       </c>
-      <c r="S40" s="50" t="n">
+      <c r="S40" s="41" t="n">
         <v>0.37</v>
       </c>
-      <c r="T40" s="50" t="n"/>
-      <c r="U40" s="50" t="n"/>
-      <c r="V40" s="50" t="n"/>
+      <c r="T40" s="41" t="n"/>
+      <c r="U40" s="41" t="n"/>
+      <c r="V40" s="41" t="n"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -4290,11 +4271,11 @@
           <t>Drive growth through Commercial Excellence</t>
         </is>
       </c>
-      <c r="K43" s="25" t="n"/>
-      <c r="L43" s="25" t="n"/>
-      <c r="M43" s="31" t="n"/>
-      <c r="N43" s="25" t="n"/>
-      <c r="O43" s="25" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
+      <c r="M43" s="27" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="24" t="n"/>
       <c r="P43" s="13" t="n"/>
       <c r="Q43" s="13" t="n"/>
       <c r="R43" s="13" t="n"/>
@@ -4360,27 +4341,27 @@
 Actual</t>
         </is>
       </c>
-      <c r="K44" s="27" t="inlineStr">
+      <c r="K44" s="25" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="L44" s="27" t="inlineStr">
+      <c r="L44" s="25" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="M44" s="32" t="inlineStr">
+      <c r="M44" s="28" t="inlineStr">
         <is>
           <t>Q1'26</t>
         </is>
       </c>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="N44" s="25" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="O44" s="27" t="inlineStr">
+      <c r="O44" s="25" t="inlineStr">
         <is>
           <t>May</t>
         </is>
@@ -4467,19 +4448,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K45" s="50" t="n">
+      <c r="K45" s="41" t="n">
         <v>0.03695155094479685</v>
       </c>
-      <c r="L45" s="50" t="n">
+      <c r="L45" s="41" t="n">
         <v>0.4362158615564438</v>
       </c>
-      <c r="M45" s="50" t="n">
+      <c r="M45" s="41" t="n">
         <v>0.06983869675270182</v>
       </c>
-      <c r="N45" s="50" t="n">
+      <c r="N45" s="41" t="n">
         <v>0.2184353977361955</v>
       </c>
-      <c r="O45" s="50" t="n">
+      <c r="O45" s="41" t="n">
         <v>0.2023926132594129</v>
       </c>
       <c r="P45" s="13" t="n">
@@ -4544,19 +4525,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K46" s="50" t="n">
+      <c r="K46" s="41" t="n">
         <v>-0.2153783747097541</v>
       </c>
-      <c r="L46" s="50" t="n">
+      <c r="L46" s="41" t="n">
         <v>0.274</v>
       </c>
-      <c r="M46" s="50" t="n">
+      <c r="M46" s="41" t="n">
         <v>0.1795699998903189</v>
       </c>
-      <c r="N46" s="50" t="n">
+      <c r="N46" s="41" t="n">
         <v>0.2402009863975842</v>
       </c>
-      <c r="O46" s="50" t="n">
+      <c r="O46" s="41" t="n">
         <v>0.1289120613896775</v>
       </c>
       <c r="P46" s="13" t="n">
@@ -4621,17 +4602,17 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K47" s="50" t="n"/>
-      <c r="L47" s="50" t="n">
+      <c r="K47" s="41" t="n"/>
+      <c r="L47" s="41" t="n">
         <v>0.09892532186664882</v>
       </c>
-      <c r="M47" s="50" t="n">
+      <c r="M47" s="41" t="n">
         <v>0.1171222837386938</v>
       </c>
-      <c r="N47" s="50" t="n">
+      <c r="N47" s="41" t="n">
         <v>0.1581</v>
       </c>
-      <c r="O47" s="50" t="n">
+      <c r="O47" s="41" t="n">
         <v>0.151</v>
       </c>
       <c r="P47" s="13" t="n">
@@ -4691,19 +4672,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K48" s="50" t="n">
+      <c r="K48" s="41" t="n">
         <v>0.325</v>
       </c>
-      <c r="L48" s="50" t="n">
+      <c r="L48" s="41" t="n">
         <v>0.1901669827329349</v>
       </c>
-      <c r="M48" s="50" t="n">
+      <c r="M48" s="41" t="n">
         <v>0.1431304298282163</v>
       </c>
-      <c r="N48" s="50" t="n">
+      <c r="N48" s="41" t="n">
         <v>0.2399</v>
       </c>
-      <c r="O48" s="50" t="n">
+      <c r="O48" s="41" t="n">
         <v>0.206</v>
       </c>
       <c r="P48" s="13" t="n">
@@ -4768,36 +4749,36 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K49" s="53" t="n">
+      <c r="K49" s="44" t="n">
         <v>8.690303799999999</v>
       </c>
-      <c r="L49" s="53" t="n">
+      <c r="L49" s="44" t="n">
         <v>14.05</v>
       </c>
-      <c r="M49" s="53" t="n">
+      <c r="M49" s="44" t="n">
         <v>24.1790697</v>
       </c>
-      <c r="N49" s="53" t="n">
+      <c r="N49" s="44" t="n">
         <v>33.5513177</v>
       </c>
-      <c r="O49" s="53" t="n">
+      <c r="O49" s="44" t="n">
         <v>41.4428498</v>
       </c>
-      <c r="P49" s="44" t="n">
+      <c r="P49" s="37" t="n">
         <v>60.82396510000001</v>
       </c>
-      <c r="Q49" s="44" t="n">
+      <c r="Q49" s="37" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="R49" s="44" t="n">
+      <c r="R49" s="37" t="n">
         <v>82.4497045</v>
       </c>
-      <c r="S49" s="44" t="n">
+      <c r="S49" s="37" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="T49" s="44" t="n"/>
-      <c r="U49" s="44" t="n"/>
-      <c r="V49" s="44" t="n"/>
+      <c r="T49" s="37" t="n"/>
+      <c r="U49" s="37" t="n"/>
+      <c r="V49" s="37" t="n"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Percentage</t>
@@ -4845,36 +4826,36 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K50" s="53" t="n">
+      <c r="K50" s="44" t="n">
         <v>4.05</v>
       </c>
-      <c r="L50" s="53" t="n">
+      <c r="L50" s="44" t="n">
         <v>9.7989724</v>
       </c>
-      <c r="M50" s="53" t="n">
+      <c r="M50" s="44" t="n">
         <v>25.3134481</v>
       </c>
-      <c r="N50" s="53" t="n">
+      <c r="N50" s="44" t="n">
         <v>31.4525575</v>
       </c>
-      <c r="O50" s="53" t="n">
+      <c r="O50" s="44" t="n">
         <v>41.12812289999999</v>
       </c>
-      <c r="P50" s="44" t="n">
+      <c r="P50" s="37" t="n">
         <v>55.164575</v>
       </c>
-      <c r="Q50" s="44" t="n">
+      <c r="Q50" s="37" t="n">
         <v>61.9402897</v>
       </c>
-      <c r="R50" s="44" t="n">
+      <c r="R50" s="37" t="n">
         <v>72.77940819999998</v>
       </c>
-      <c r="S50" s="44" t="n">
+      <c r="S50" s="37" t="n">
         <v>91.2</v>
       </c>
-      <c r="T50" s="44" t="n"/>
-      <c r="U50" s="44" t="n"/>
-      <c r="V50" s="44" t="n"/>
+      <c r="T50" s="37" t="n"/>
+      <c r="U50" s="37" t="n"/>
+      <c r="V50" s="37" t="n"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Percentage</t>
@@ -4932,42 +4913,42 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
-      <c r="M51" s="50" t="n">
+      <c r="K51" s="41" t="n"/>
+      <c r="L51" s="41" t="n"/>
+      <c r="M51" s="41" t="n">
         <v>0.104</v>
       </c>
-      <c r="N51" s="50" t="inlineStr">
+      <c r="N51" s="41" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="O51" s="50" t="inlineStr">
+      <c r="O51" s="41" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="P51" s="50" t="n">
+      <c r="P51" s="41" t="n">
         <v>0.118</v>
       </c>
-      <c r="Q51" s="50" t="inlineStr">
+      <c r="Q51" s="41" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="R51" s="50" t="inlineStr">
+      <c r="R51" s="41" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="S51" s="50" t="inlineStr">
+      <c r="S51" s="41" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="T51" s="50" t="n"/>
-      <c r="U51" s="50" t="n"/>
-      <c r="V51" s="50" t="n"/>
+      <c r="T51" s="41" t="n"/>
+      <c r="U51" s="41" t="n"/>
+      <c r="V51" s="41" t="n"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -5025,30 +5006,30 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K52" s="40" t="inlineStr">
+      <c r="K52" s="33" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="L52" s="40" t="inlineStr">
+      <c r="L52" s="33" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="M52" s="40" t="n">
+      <c r="M52" s="33" t="n">
         <v>0.115</v>
       </c>
-      <c r="N52" s="41" t="inlineStr">
+      <c r="N52" s="34" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="O52" s="40" t="inlineStr">
+      <c r="O52" s="33" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="P52" s="39" t="n">
+      <c r="P52" s="32" t="n">
         <v>0.12</v>
       </c>
       <c r="Q52" s="8" t="inlineStr">
@@ -5240,12 +5221,12 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K56" s="33" t="n"/>
-      <c r="L56" s="33" t="n"/>
-      <c r="M56" s="33" t="n">
+      <c r="K56" s="29" t="n"/>
+      <c r="L56" s="29" t="n"/>
+      <c r="M56" s="29" t="n">
         <v>0.9</v>
       </c>
-      <c r="N56" s="33" t="n"/>
+      <c r="N56" s="29" t="n"/>
       <c r="O56" s="12" t="n"/>
       <c r="P56" s="12" t="n">
         <v>0.9</v>
@@ -5305,20 +5286,20 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K57" s="33" t="inlineStr">
+      <c r="K57" s="29" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="L57" s="33" t="inlineStr">
+      <c r="L57" s="29" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
       </c>
-      <c r="M57" s="33" t="n">
+      <c r="M57" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="N57" s="33" t="inlineStr">
+      <c r="N57" s="29" t="inlineStr">
         <is>
           <t>QTR</t>
         </is>
@@ -5392,10 +5373,10 @@
           <t>T</t>
         </is>
       </c>
-      <c r="K58" s="33" t="n"/>
-      <c r="L58" s="33" t="n"/>
-      <c r="M58" s="33" t="n"/>
-      <c r="N58" s="33" t="n">
+      <c r="K58" s="29" t="n"/>
+      <c r="L58" s="29" t="n"/>
+      <c r="M58" s="29" t="n"/>
+      <c r="N58" s="29" t="n">
         <v>0.83</v>
       </c>
       <c r="O58" s="12" t="n"/>
@@ -5453,22 +5434,22 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K59" s="33" t="inlineStr">
+      <c r="K59" s="29" t="inlineStr">
         <is>
           <t>HY</t>
         </is>
       </c>
-      <c r="L59" s="33" t="inlineStr">
+      <c r="L59" s="29" t="inlineStr">
         <is>
           <t>HY</t>
         </is>
       </c>
-      <c r="M59" s="33" t="inlineStr">
+      <c r="M59" s="29" t="inlineStr">
         <is>
           <t>HY</t>
         </is>
       </c>
-      <c r="N59" s="33" t="n">
+      <c r="N59" s="29" t="n">
         <v>0.79</v>
       </c>
       <c r="O59" s="12" t="inlineStr">
@@ -5519,23 +5500,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V200"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="43.42578125" customWidth="1" min="1" max="5"/>
-    <col width="15.42578125" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="43.42578125" customWidth="1" min="7" max="11"/>
-    <col hidden="1" width="35.5703125" customWidth="1" min="12" max="12"/>
-    <col hidden="1" width="11.42578125" customWidth="1" min="13" max="13"/>
-    <col width="11.42578125" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="10.85546875" customWidth="1" min="15" max="15"/>
-    <col width="11.42578125" customWidth="1" min="16" max="16"/>
-    <col width="9.42578125" bestFit="1" customWidth="1" min="17" max="19"/>
-    <col width="11.85546875" bestFit="1" customWidth="1" min="20" max="20"/>
-    <col width="12.7109375" bestFit="1" customWidth="1" min="21" max="21"/>
-    <col width="17.85546875" bestFit="1" customWidth="1" min="22" max="22"/>
+    <col width="43.453125" customWidth="1" min="1" max="5"/>
+    <col width="15.453125" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="43.453125" customWidth="1" min="7" max="11"/>
+    <col hidden="1" width="35.54296875" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="11.453125" customWidth="1" min="13" max="13"/>
+    <col width="11.453125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="10.81640625" customWidth="1" min="15" max="15"/>
+    <col width="11.453125" customWidth="1" min="16" max="16"/>
+    <col width="9.453125" bestFit="1" customWidth="1" min="17" max="19"/>
+    <col width="11.81640625" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="12.7265625" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="17.81640625" bestFit="1" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.6" customHeight="1">
+    <row r="1" ht="18.65" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Mastersheet</t>
@@ -5953,19 +5934,19 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="16" t="n">
         <v>4</v>
       </c>
       <c r="N8" t="n">
@@ -8580,7 +8561,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V41" s="21" t="inlineStr">
+      <c r="V41" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -8660,7 +8641,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V42" s="19" t="inlineStr">
+      <c r="V42" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -8748,7 +8729,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V43" s="21" t="inlineStr">
+      <c r="V43" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -8827,7 +8808,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V44" s="19" t="inlineStr">
+      <c r="V44" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -8913,7 +8894,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V45" s="21" t="inlineStr">
+      <c r="V45" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -8993,7 +8974,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V46" s="19" t="inlineStr">
+      <c r="V46" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9087,7 +9068,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V47" s="21" t="inlineStr">
+      <c r="V47" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9181,7 +9162,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V48" s="19" t="inlineStr">
+      <c r="V48" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9269,7 +9250,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V49" s="21" t="inlineStr">
+      <c r="V49" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9351,7 +9332,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V50" s="19" t="inlineStr">
+      <c r="V50" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9437,7 +9418,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V51" s="19" t="inlineStr">
+      <c r="V51" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9517,7 +9498,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V52" s="19" t="inlineStr">
+      <c r="V52" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -9605,7 +9586,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V53" s="19" t="inlineStr">
+      <c r="V53" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -9687,7 +9668,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V54" s="19" t="inlineStr">
+      <c r="V54" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -9773,7 +9754,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V55" s="19" t="inlineStr">
+      <c r="V55" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -9853,7 +9834,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V56" s="19" t="inlineStr">
+      <c r="V56" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -9941,7 +9922,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V57" s="19" t="inlineStr">
+      <c r="V57" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10023,7 +10004,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V58" s="19" t="inlineStr">
+      <c r="V58" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10068,40 +10049,40 @@
           <t xml:space="preserve">Target </t>
         </is>
       </c>
-      <c r="I59" s="17" t="n">
+      <c r="I59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="J59" s="17" t="n">
+      <c r="J59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="K59" s="17" t="n">
+      <c r="K59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="L59" s="17" t="n">
+      <c r="L59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="M59" s="17" t="n">
+      <c r="M59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="N59" s="17" t="n">
+      <c r="N59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="O59" s="17" t="n">
+      <c r="O59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="P59" s="17" t="n">
+      <c r="P59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="Q59" s="17" t="n">
+      <c r="Q59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="R59" s="17" t="n">
+      <c r="R59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="S59" s="17" t="n">
+      <c r="S59" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="T59" s="17" t="n">
+      <c r="T59" s="16" t="n">
         <v>15</v>
       </c>
       <c r="U59" t="inlineStr">
@@ -10109,7 +10090,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V59" s="19" t="inlineStr">
+      <c r="V59" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10183,7 +10164,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V60" s="19" t="inlineStr">
+      <c r="V60" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10270,7 +10251,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V61" s="19" t="inlineStr">
+      <c r="V61" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10349,7 +10330,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V62" s="19" t="inlineStr">
+      <c r="V62" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10435,7 +10416,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V63" s="19" t="inlineStr">
+      <c r="V63" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10513,7 +10494,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V64" s="19" t="inlineStr">
+      <c r="V64" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10599,7 +10580,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V65" s="19" t="inlineStr">
+      <c r="V65" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10677,13 +10658,13 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V66" s="19" t="inlineStr">
+      <c r="V66" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="14.1" customHeight="1">
+    <row r="67" ht="14.15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
           <t>DEFOA</t>
@@ -10754,7 +10735,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V67" s="19" t="inlineStr">
+      <c r="V67" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10805,16 +10786,16 @@
       <c r="J68" s="7" t="n">
         <v>0.04</v>
       </c>
-      <c r="K68" s="42" t="n">
+      <c r="K68" s="35" t="n">
         <v>0.006</v>
       </c>
-      <c r="L68" s="42" t="n">
+      <c r="L68" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="M68" s="18" t="n">
+      <c r="M68" s="17" t="n">
         <v>0.02</v>
       </c>
-      <c r="N68" s="18" t="n">
+      <c r="N68" s="17" t="n">
         <v>0.013</v>
       </c>
       <c r="O68" s="7" t="n">
@@ -10831,7 +10812,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V68" s="19" t="inlineStr">
+      <c r="V68" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10917,7 +10898,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V69" s="19" t="inlineStr">
+      <c r="V69" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -10997,7 +10978,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V70" s="19" t="inlineStr">
+      <c r="V70" s="18" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -11614,16 +11595,16 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I78" s="18" t="n">
+      <c r="I78" s="17" t="n">
         <v>0.020673</v>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="J78" s="17" t="n">
         <v>0.058772</v>
       </c>
-      <c r="K78" s="18" t="n">
+      <c r="K78" s="17" t="n">
         <v>0.105659</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="L78" s="17" t="n">
         <v>0.152422</v>
       </c>
       <c r="M78" t="n">
@@ -11857,40 +11838,40 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I81" s="20" t="n">
+      <c r="I81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="20" t="n">
+      <c r="J81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K81" s="20" t="n">
+      <c r="K81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="20" t="n">
+      <c r="L81" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M81" s="20" t="n">
+      <c r="M81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N81" s="20" t="n">
+      <c r="N81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="O81" s="20" t="n">
+      <c r="O81" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="P81" s="20" t="n">
+      <c r="P81" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" s="20" t="n">
+      <c r="Q81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R81" s="20" t="n">
+      <c r="R81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="20" t="n">
+      <c r="S81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="T81" s="20" t="n">
+      <c r="T81" s="19" t="n">
         <v>0</v>
       </c>
       <c r="U81" t="inlineStr">
@@ -11943,24 +11924,24 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I82" s="34" t="n"/>
-      <c r="J82" s="34" t="n"/>
-      <c r="K82" s="34" t="n"/>
-      <c r="L82" s="34" t="n"/>
-      <c r="M82" s="34" t="n"/>
-      <c r="N82" s="34" t="n"/>
-      <c r="O82" s="20" t="n">
+      <c r="I82" s="30" t="n"/>
+      <c r="J82" s="30" t="n"/>
+      <c r="K82" s="30" t="n"/>
+      <c r="L82" s="30" t="n"/>
+      <c r="M82" s="30" t="n"/>
+      <c r="N82" s="30" t="n"/>
+      <c r="O82" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="P82" s="20" t="n">
+      <c r="P82" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" s="20" t="n">
+      <c r="Q82" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R82" s="34" t="n"/>
-      <c r="S82" s="34" t="n"/>
-      <c r="T82" s="34" t="n"/>
+      <c r="R82" s="30" t="n"/>
+      <c r="S82" s="30" t="n"/>
+      <c r="T82" s="30" t="n"/>
       <c r="U82" t="inlineStr">
         <is>
           <t>Percentage</t>
@@ -12097,7 +12078,7 @@
           <t>NPI  -Design Maturity Index (%)</t>
         </is>
       </c>
-      <c r="B85" s="43" t="inlineStr">
+      <c r="B85" s="36" t="inlineStr">
         <is>
           <t>% of design Completion with zero major Quality Issues
 1) Design Maturity 
@@ -12174,7 +12155,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V85" s="21" t="inlineStr">
+      <c r="V85" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12186,7 +12167,7 @@
           <t>NPI  -Design Maturity Index (%)</t>
         </is>
       </c>
-      <c r="B86" s="43" t="inlineStr">
+      <c r="B86" s="36" t="inlineStr">
         <is>
           <t>% of design Completion with zero major Quality Issues
 1) Design Maturity 
@@ -12254,7 +12235,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V86" s="19" t="inlineStr">
+      <c r="V86" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12342,7 +12323,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V87" s="21" t="inlineStr">
+      <c r="V87" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12421,7 +12402,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V88" s="19" t="inlineStr">
+      <c r="V88" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12502,7 +12483,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V89" s="21" t="inlineStr">
+      <c r="V89" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12580,7 +12561,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V90" s="19" t="inlineStr">
+      <c r="V90" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12656,7 +12637,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V91" s="19" t="inlineStr">
+      <c r="V91" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12729,7 +12710,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V92" s="19" t="inlineStr">
+      <c r="V92" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12751,7 +12732,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="inlineStr">
@@ -12800,7 +12781,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V93" s="19" t="inlineStr">
+      <c r="V93" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12822,7 +12803,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="inlineStr">
@@ -12871,7 +12852,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V94" s="19" t="inlineStr">
+      <c r="V94" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -12957,7 +12938,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V95" s="21" t="inlineStr">
+      <c r="V95" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -13033,7 +13014,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V96" s="19" t="inlineStr">
+      <c r="V96" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -13332,7 +13313,7 @@
       <c r="I100" t="n">
         <v>80</v>
       </c>
-      <c r="J100" s="17" t="n">
+      <c r="J100" s="16" t="n">
         <v>67</v>
       </c>
       <c r="K100" t="n">
@@ -13688,42 +13669,42 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I105" s="17" t="n">
+      <c r="I105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="J105" s="17" t="n">
+      <c r="J105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="K105" s="17" t="inlineStr">
+      <c r="K105" s="16" t="inlineStr">
         <is>
           <t>Sales tool delivery</t>
         </is>
       </c>
-      <c r="L105" s="17" t="n">
+      <c r="L105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="M105" s="17" t="n">
+      <c r="M105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="N105" s="17" t="n">
+      <c r="N105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="O105" s="17" t="n">
+      <c r="O105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="P105" s="17" t="n">
+      <c r="P105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="Q105" s="17" t="n">
+      <c r="Q105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="R105" s="17" t="n">
+      <c r="R105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="S105" s="17" t="n">
+      <c r="S105" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="T105" s="17" t="n">
+      <c r="T105" s="16" t="n">
         <v>80</v>
       </c>
       <c r="U105" t="inlineStr">
@@ -13731,7 +13712,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V105" s="21" t="inlineStr">
+      <c r="V105" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -13776,42 +13757,42 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I106" s="17" t="n">
+      <c r="I106" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="J106" s="17" t="n">
+      <c r="J106" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="K106" s="17" t="n">
+      <c r="K106" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="L106" s="17" t="n">
+      <c r="L106" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="M106" s="17" t="n">
+      <c r="M106" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="N106" s="17" t="n">
+      <c r="N106" s="16" t="n">
         <v>83</v>
       </c>
-      <c r="O106" s="17" t="n">
+      <c r="O106" s="16" t="n">
         <v>77</v>
       </c>
-      <c r="P106" s="17" t="n">
+      <c r="P106" s="16" t="n">
         <v>77</v>
       </c>
-      <c r="Q106" s="17" t="n">
+      <c r="Q106" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="R106" s="17" t="n"/>
-      <c r="S106" s="17" t="n"/>
-      <c r="T106" s="17" t="n"/>
+      <c r="R106" s="16" t="n"/>
+      <c r="S106" s="16" t="n"/>
+      <c r="T106" s="16" t="n"/>
       <c r="U106" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V106" s="19" t="inlineStr">
+      <c r="V106" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -13899,7 +13880,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V107" s="21" t="inlineStr">
+      <c r="V107" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -13976,7 +13957,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V108" s="19" t="inlineStr">
+      <c r="V108" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -14064,7 +14045,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V109" s="21" t="inlineStr">
+      <c r="V109" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -14141,7 +14122,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V110" s="19" t="inlineStr">
+      <c r="V110" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -14229,7 +14210,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V111" s="22" t="inlineStr">
+      <c r="V111" s="21" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -14309,7 +14290,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V112" s="23" t="inlineStr">
+      <c r="V112" s="22" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -14397,7 +14378,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V113" s="22" t="inlineStr">
+      <c r="V113" s="21" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -14473,7 +14454,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V114" s="23" t="inlineStr">
+      <c r="V114" s="22" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -14557,7 +14538,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V115" s="22" t="inlineStr">
+      <c r="V115" s="21" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -14633,7 +14614,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V116" s="23" t="inlineStr">
+      <c r="V116" s="22" t="inlineStr">
         <is>
           <t>Mandatory Outcome</t>
         </is>
@@ -14840,7 +14821,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V119" s="21" t="inlineStr">
+      <c r="V119" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -14920,7 +14901,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V120" s="19" t="inlineStr">
+      <c r="V120" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15008,7 +14989,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V121" s="21" t="inlineStr">
+      <c r="V121" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15088,7 +15069,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V122" s="19" t="inlineStr">
+      <c r="V122" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15176,7 +15157,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V123" s="21" t="inlineStr">
+      <c r="V123" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15253,7 +15234,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V124" s="19" t="inlineStr">
+      <c r="V124" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15341,7 +15322,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V125" s="21" t="inlineStr">
+      <c r="V125" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15418,7 +15399,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V126" s="19" t="inlineStr">
+      <c r="V126" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15440,7 +15421,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D127" s="45" t="n">
+      <c r="D127" s="38" t="n">
         <v>0.236</v>
       </c>
       <c r="E127" t="inlineStr">
@@ -15506,7 +15487,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V127" s="21" t="inlineStr">
+      <c r="V127" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15528,7 +15509,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D128" s="45" t="n">
+      <c r="D128" s="38" t="n">
         <v>0.236</v>
       </c>
       <c r="E128" t="inlineStr">
@@ -15586,7 +15567,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V128" s="19" t="inlineStr">
+      <c r="V128" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15608,7 +15589,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D129" s="45" t="n">
+      <c r="D129" s="38" t="n">
         <v>0.8159999999999999</v>
       </c>
       <c r="E129" t="inlineStr">
@@ -15674,7 +15655,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V129" s="21" t="inlineStr">
+      <c r="V129" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15696,7 +15677,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D130" s="45" t="n">
+      <c r="D130" s="38" t="n">
         <v>0.8159999999999999</v>
       </c>
       <c r="E130" t="inlineStr">
@@ -15754,7 +15735,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V130" s="19" t="inlineStr">
+      <c r="V130" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15842,7 +15823,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V131" s="21" t="inlineStr">
+      <c r="V131" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -15922,7 +15903,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V132" s="19" t="inlineStr">
+      <c r="V132" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -16107,38 +16088,38 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I135" s="20" t="n">
+      <c r="I135" s="19" t="n">
         <v>5.87</v>
       </c>
-      <c r="J135" s="20" t="n">
+      <c r="J135" s="19" t="n">
         <v>11.52</v>
       </c>
-      <c r="K135" s="20" t="inlineStr">
+      <c r="K135" s="19" t="inlineStr">
         <is>
           <t>CS Revenue</t>
         </is>
       </c>
-      <c r="L135" s="20" t="n">
+      <c r="L135" s="19" t="n">
         <v>24.1</v>
       </c>
-      <c r="M135" s="20" t="n">
+      <c r="M135" s="19" t="n">
         <v>30.33</v>
       </c>
-      <c r="N135" s="20" t="n">
+      <c r="N135" s="19" t="n">
         <v>36.89</v>
       </c>
-      <c r="O135" s="20" t="n">
+      <c r="O135" s="19" t="n">
         <v>43.25</v>
       </c>
-      <c r="P135" s="20" t="n">
+      <c r="P135" s="19" t="n">
         <v>49.6</v>
       </c>
-      <c r="Q135" s="20" t="n">
+      <c r="Q135" s="19" t="n">
         <v>56.24</v>
       </c>
-      <c r="R135" s="20" t="n"/>
-      <c r="S135" s="20" t="n"/>
-      <c r="T135" s="20" t="n"/>
+      <c r="R135" s="19" t="n"/>
+      <c r="S135" s="19" t="n"/>
+      <c r="T135" s="19" t="n"/>
       <c r="U135" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -16189,36 +16170,36 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I136" s="20" t="n">
+      <c r="I136" s="19" t="n">
         <v>5.77</v>
       </c>
-      <c r="J136" s="20" t="n">
+      <c r="J136" s="19" t="n">
         <v>11.29</v>
       </c>
-      <c r="K136" s="20" t="n">
+      <c r="K136" s="19" t="n">
         <v>17.7</v>
       </c>
-      <c r="L136" s="44" t="n">
+      <c r="L136" s="37" t="n">
         <v>23.77</v>
       </c>
-      <c r="M136" s="20" t="n">
+      <c r="M136" s="19" t="n">
         <v>29.8</v>
       </c>
-      <c r="N136" s="20" t="n">
+      <c r="N136" s="19" t="n">
         <v>36.26</v>
       </c>
-      <c r="O136" s="20" t="n">
+      <c r="O136" s="19" t="n">
         <v>42.54</v>
       </c>
-      <c r="P136" s="20" t="n">
+      <c r="P136" s="19" t="n">
         <v>48.8</v>
       </c>
-      <c r="Q136" s="20" t="n">
+      <c r="Q136" s="19" t="n">
         <v>55.4</v>
       </c>
-      <c r="R136" s="20" t="n"/>
-      <c r="S136" s="20" t="n"/>
-      <c r="T136" s="20" t="n"/>
+      <c r="R136" s="19" t="n"/>
+      <c r="S136" s="19" t="n"/>
+      <c r="T136" s="19" t="n"/>
       <c r="U136" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -16246,7 +16227,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D137" s="45" t="n">
+      <c r="D137" s="38" t="n">
         <v>0.527</v>
       </c>
       <c r="E137" t="inlineStr">
@@ -16334,7 +16315,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D138" s="45" t="n">
+      <c r="D138" s="38" t="n">
         <v>0.527</v>
       </c>
       <c r="E138" t="inlineStr">
@@ -16599,7 +16580,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V141" s="21" t="inlineStr">
+      <c r="V141" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -16675,7 +16656,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V142" s="19" t="inlineStr">
+      <c r="V142" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -16761,7 +16742,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V143" s="21" t="inlineStr">
+      <c r="V143" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -16832,7 +16813,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V144" s="19" t="inlineStr">
+      <c r="V144" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -16918,7 +16899,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V145" s="21" t="inlineStr">
+      <c r="V145" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -16963,16 +16944,16 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I146" s="17" t="n">
+      <c r="I146" s="16" t="n">
         <v>85.7</v>
       </c>
-      <c r="J146" s="17" t="n">
+      <c r="J146" s="16" t="n">
         <v>61.5</v>
       </c>
-      <c r="K146" s="17" t="n">
+      <c r="K146" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="L146" s="17" t="n">
+      <c r="L146" s="16" t="n">
         <v>38.5</v>
       </c>
       <c r="M146" t="n">
@@ -16994,7 +16975,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V146" s="19" t="inlineStr">
+      <c r="V146" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17080,7 +17061,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V147" s="21" t="inlineStr">
+      <c r="V147" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17148,7 +17129,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V148" s="19" t="inlineStr">
+      <c r="V148" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17234,7 +17215,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V149" s="21" t="inlineStr">
+      <c r="V149" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17310,7 +17291,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V150" s="19" t="inlineStr">
+      <c r="V150" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17396,7 +17377,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V151" s="21" t="inlineStr">
+      <c r="V151" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17472,7 +17453,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V152" s="19" t="inlineStr">
+      <c r="V152" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -17673,42 +17654,42 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I155" s="24" t="n">
+      <c r="I155" s="23" t="n">
         <v>2.4</v>
       </c>
-      <c r="J155" s="24" t="n">
+      <c r="J155" s="23" t="n">
         <v>2.4</v>
       </c>
-      <c r="K155" s="24" t="inlineStr">
+      <c r="K155" s="23" t="inlineStr">
         <is>
           <t>€40</t>
         </is>
       </c>
-      <c r="L155" s="24" t="n">
+      <c r="L155" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="M155" s="24" t="n">
+      <c r="M155" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="N155" s="24" t="n">
+      <c r="N155" s="23" t="n">
         <v>4.8</v>
       </c>
-      <c r="O155" s="24" t="n">
+      <c r="O155" s="23" t="n">
         <v>2.8</v>
       </c>
-      <c r="P155" s="24" t="n">
+      <c r="P155" s="23" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q155" s="24" t="n">
+      <c r="Q155" s="23" t="n">
         <v>5.6</v>
       </c>
-      <c r="R155" s="24" t="n">
+      <c r="R155" s="23" t="n">
         <v>3.7</v>
       </c>
-      <c r="S155" s="24" t="n">
+      <c r="S155" s="23" t="n">
         <v>4.1</v>
       </c>
-      <c r="T155" s="24" t="n">
+      <c r="T155" s="23" t="n">
         <v>4.2</v>
       </c>
       <c r="U155" t="inlineStr">
@@ -17763,32 +17744,32 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I156" s="24" t="n">
+      <c r="I156" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="J156" s="24" t="n">
+      <c r="J156" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="K156" s="24" t="n">
+      <c r="K156" s="23" t="n">
         <v>3.1</v>
       </c>
-      <c r="L156" s="24" t="n">
+      <c r="L156" s="23" t="n">
         <v>4.1</v>
       </c>
-      <c r="M156" s="24" t="n">
+      <c r="M156" s="23" t="n">
         <v>2.6</v>
       </c>
-      <c r="N156" s="24" t="n">
+      <c r="N156" s="23" t="n">
         <v>3.2</v>
       </c>
-      <c r="O156" s="24" t="n">
+      <c r="O156" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="P156" s="24" t="n"/>
-      <c r="Q156" s="24" t="n"/>
-      <c r="R156" s="24" t="n"/>
-      <c r="S156" s="24" t="n"/>
-      <c r="T156" s="24" t="n"/>
+      <c r="P156" s="23" t="n"/>
+      <c r="Q156" s="23" t="n"/>
+      <c r="R156" s="23" t="n"/>
+      <c r="S156" s="23" t="n"/>
+      <c r="T156" s="23" t="n"/>
       <c r="U156" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -17841,42 +17822,42 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I157" s="46" t="n">
+      <c r="I157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="J157" s="46" t="n">
+      <c r="J157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="K157" s="46" t="inlineStr">
+      <c r="K157" s="39" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="L157" s="46" t="n">
+      <c r="L157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="M157" s="46" t="n">
+      <c r="M157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="N157" s="46" t="n">
+      <c r="N157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="O157" s="46" t="n">
+      <c r="O157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="P157" s="46" t="n">
+      <c r="P157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="Q157" s="46" t="n">
+      <c r="Q157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="R157" s="46" t="n">
+      <c r="R157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="S157" s="46" t="n">
+      <c r="S157" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="T157" s="46" t="n">
+      <c r="T157" s="39" t="n">
         <v>40</v>
       </c>
       <c r="U157" t="inlineStr">
@@ -17931,28 +17912,28 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I158" s="24" t="n">
+      <c r="I158" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="J158" s="24" t="n">
+      <c r="J158" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="K158" s="24" t="n">
+      <c r="K158" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="L158" s="24" t="n">
+      <c r="L158" s="23" t="n">
         <v>68</v>
       </c>
-      <c r="M158" s="24" t="n">
+      <c r="M158" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="N158" s="24" t="n"/>
-      <c r="O158" s="24" t="n"/>
-      <c r="P158" s="24" t="n"/>
-      <c r="Q158" s="24" t="n"/>
-      <c r="R158" s="24" t="n"/>
-      <c r="S158" s="24" t="n"/>
-      <c r="T158" s="24" t="n"/>
+      <c r="N158" s="23" t="n"/>
+      <c r="O158" s="23" t="n"/>
+      <c r="P158" s="23" t="n"/>
+      <c r="Q158" s="23" t="n"/>
+      <c r="R158" s="23" t="n"/>
+      <c r="S158" s="23" t="n"/>
+      <c r="T158" s="23" t="n"/>
       <c r="U158" t="inlineStr">
         <is>
           <t>Percentage</t>
@@ -18167,7 +18148,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V161" s="21" t="inlineStr">
+      <c r="V161" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18243,7 +18224,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V162" s="19" t="inlineStr">
+      <c r="V162" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18265,7 +18246,7 @@
           <t>=</t>
         </is>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="16" t="n">
         <v>10</v>
       </c>
       <c r="E163" t="inlineStr">
@@ -18333,7 +18314,7 @@
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V163" s="21" t="inlineStr">
+      <c r="V163" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18355,7 +18336,7 @@
           <t>=</t>
         </is>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="16" t="n">
         <v>10</v>
       </c>
       <c r="E164" t="inlineStr">
@@ -18405,15 +18386,15 @@
       <c r="Q164" s="12" t="n">
         <v>0.67</v>
       </c>
-      <c r="R164" s="35" t="n"/>
-      <c r="S164" s="35" t="n"/>
-      <c r="T164" s="35" t="n"/>
+      <c r="R164" s="31" t="n"/>
+      <c r="S164" s="31" t="n"/>
+      <c r="T164" s="31" t="n"/>
       <c r="U164" t="inlineStr">
         <is>
           <t>Whole Number</t>
         </is>
       </c>
-      <c r="V164" s="19" t="inlineStr">
+      <c r="V164" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18499,7 +18480,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V165" s="21" t="inlineStr">
+      <c r="V165" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -18577,7 +18558,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V166" s="19" t="inlineStr">
+      <c r="V166" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -18667,7 +18648,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V167" s="21" t="inlineStr">
+      <c r="V167" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18743,7 +18724,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V168" s="19" t="inlineStr">
+      <c r="V168" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18765,7 +18746,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D169" s="45" t="n">
+      <c r="D169" s="38" t="n">
         <v>0.413</v>
       </c>
       <c r="E169" t="inlineStr">
@@ -18833,7 +18814,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V169" s="21" t="inlineStr">
+      <c r="V169" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18855,7 +18836,7 @@
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="D170" s="45" t="n">
+      <c r="D170" s="38" t="n">
         <v>0.413</v>
       </c>
       <c r="E170" t="inlineStr">
@@ -18911,7 +18892,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V170" s="19" t="inlineStr">
+      <c r="V170" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -18933,7 +18914,7 @@
           <t>=</t>
         </is>
       </c>
-      <c r="D171" s="45" t="n">
+      <c r="D171" s="38" t="n">
         <v>0.165</v>
       </c>
       <c r="E171" t="inlineStr">
@@ -19005,7 +18986,7 @@
           <t>=</t>
         </is>
       </c>
-      <c r="D172" s="45" t="n">
+      <c r="D172" s="38" t="n">
         <v>0.165</v>
       </c>
       <c r="E172" t="inlineStr">
@@ -19094,40 +19075,40 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I173" s="20" t="n">
+      <c r="I173" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J173" s="20" t="n">
+      <c r="J173" s="19" t="n">
         <v>1.6</v>
       </c>
-      <c r="K173" s="20" t="n">
+      <c r="K173" s="19" t="n">
         <v>3.9</v>
       </c>
-      <c r="L173" s="20" t="n">
+      <c r="L173" s="19" t="n">
         <v>3.1</v>
       </c>
-      <c r="M173" s="20" t="n">
+      <c r="M173" s="19" t="n">
         <v>2.1</v>
       </c>
-      <c r="N173" s="20" t="n">
+      <c r="N173" s="19" t="n">
         <v>4.4</v>
       </c>
-      <c r="O173" s="20" t="n">
+      <c r="O173" s="19" t="n">
         <v>2.9</v>
       </c>
-      <c r="P173" s="20" t="n">
+      <c r="P173" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="Q173" s="20" t="n">
+      <c r="Q173" s="19" t="n">
         <v>4.5</v>
       </c>
-      <c r="R173" s="20" t="n">
+      <c r="R173" s="19" t="n">
         <v>3.8</v>
       </c>
-      <c r="S173" s="20" t="n">
+      <c r="S173" s="19" t="n">
         <v>4.7</v>
       </c>
-      <c r="T173" s="20" t="n">
+      <c r="T173" s="19" t="n">
         <v>7.1</v>
       </c>
       <c r="U173" t="inlineStr">
@@ -19180,34 +19161,34 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I174" s="20" t="n">
+      <c r="I174" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J174" s="20" t="n">
+      <c r="J174" s="19" t="n">
         <v>2.9</v>
       </c>
-      <c r="K174" s="20" t="n">
+      <c r="K174" s="19" t="n">
         <v>5.4</v>
       </c>
-      <c r="L174" s="20" t="n">
+      <c r="L174" s="19" t="n">
         <v>1.9</v>
       </c>
-      <c r="M174" s="20" t="n">
+      <c r="M174" s="19" t="n">
         <v>1.7</v>
       </c>
-      <c r="N174" s="20" t="n">
+      <c r="N174" s="19" t="n">
         <v>4.4</v>
       </c>
-      <c r="O174" s="20" t="n">
+      <c r="O174" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="P174" s="20" t="n">
+      <c r="P174" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q174" s="20" t="n"/>
-      <c r="R174" s="20" t="n"/>
-      <c r="S174" s="20" t="n"/>
-      <c r="T174" s="20" t="n"/>
+      <c r="Q174" s="19" t="n"/>
+      <c r="R174" s="19" t="n"/>
+      <c r="S174" s="19" t="n"/>
+      <c r="T174" s="19" t="n"/>
       <c r="U174" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -19258,40 +19239,40 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I175" s="20" t="n">
+      <c r="I175" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="J175" s="20" t="n">
+      <c r="J175" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="K175" s="20" t="n">
+      <c r="K175" s="19" t="n">
         <v>3.5</v>
       </c>
-      <c r="L175" s="20" t="n">
+      <c r="L175" s="19" t="n">
         <v>1.8</v>
       </c>
-      <c r="M175" s="20" t="n">
+      <c r="M175" s="19" t="n">
         <v>1.8</v>
       </c>
-      <c r="N175" s="20" t="n">
+      <c r="N175" s="19" t="n">
         <v>1.8</v>
       </c>
-      <c r="O175" s="20" t="n">
+      <c r="O175" s="19" t="n">
         <v>1.7</v>
       </c>
-      <c r="P175" s="20" t="n">
+      <c r="P175" s="19" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q175" s="20" t="n">
+      <c r="Q175" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="R175" s="20" t="n">
+      <c r="R175" s="19" t="n">
         <v>2.4</v>
       </c>
-      <c r="S175" s="20" t="n">
+      <c r="S175" s="19" t="n">
         <v>2.3</v>
       </c>
-      <c r="T175" s="20" t="n">
+      <c r="T175" s="19" t="n">
         <v>3.7</v>
       </c>
       <c r="U175" t="inlineStr">
@@ -19344,34 +19325,34 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I176" s="20" t="n">
+      <c r="I176" s="19" t="n">
         <v>2.6</v>
       </c>
-      <c r="J176" s="20" t="n">
+      <c r="J176" s="19" t="n">
         <v>1.9</v>
       </c>
-      <c r="K176" s="20" t="n">
+      <c r="K176" s="19" t="n">
         <v>3.6</v>
       </c>
-      <c r="L176" s="20" t="n">
+      <c r="L176" s="19" t="n">
         <v>2.9</v>
       </c>
-      <c r="M176" s="20" t="n">
+      <c r="M176" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="N176" s="20" t="n">
+      <c r="N176" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="O176" s="20" t="n">
+      <c r="O176" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="P176" s="20" t="n">
+      <c r="P176" s="19" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q176" s="20" t="n"/>
-      <c r="R176" s="20" t="n"/>
-      <c r="S176" s="20" t="n"/>
-      <c r="T176" s="20" t="n"/>
+      <c r="Q176" s="19" t="n"/>
+      <c r="R176" s="19" t="n"/>
+      <c r="S176" s="19" t="n"/>
+      <c r="T176" s="19" t="n"/>
       <c r="U176" t="inlineStr">
         <is>
           <t>Decimal</t>
@@ -19422,44 +19403,44 @@
           <t>Target</t>
         </is>
       </c>
-      <c r="I177" s="20" t="n">
+      <c r="I177" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="J177" s="20" t="n">
+      <c r="J177" s="19" t="n">
         <v>4.800000000000001</v>
       </c>
-      <c r="K177" s="20" t="inlineStr">
+      <c r="K177" s="19" t="inlineStr">
         <is>
           <t>EQ Funnel Sufficiency</t>
         </is>
       </c>
-      <c r="L177" s="20" t="n">
+      <c r="L177" s="19" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="M177" s="20" t="n">
+      <c r="M177" s="19" t="n">
         <v>6.300000000000001</v>
       </c>
-      <c r="N177" s="20" t="n">
+      <c r="N177" s="19" t="n">
         <v>13.2</v>
       </c>
-      <c r="O177" s="20" t="inlineStr">
+      <c r="O177" s="19" t="inlineStr">
         <is>
           <t>Higher the better</t>
         </is>
       </c>
-      <c r="P177" s="20" t="n">
+      <c r="P177" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="Q177" s="20" t="n">
+      <c r="Q177" s="19" t="n">
         <v>13.5</v>
       </c>
-      <c r="R177" s="20" t="n">
+      <c r="R177" s="19" t="n">
         <v>11.4</v>
       </c>
-      <c r="S177" s="20" t="n">
+      <c r="S177" s="19" t="n">
         <v>14.1</v>
       </c>
-      <c r="T177" s="20" t="n">
+      <c r="T177" s="19" t="n">
         <v>21.3</v>
       </c>
       <c r="U177" t="inlineStr">
@@ -19512,36 +19493,36 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="I178" s="20" t="n">
+      <c r="I178" s="19" t="n">
         <v>4.6</v>
       </c>
-      <c r="J178" s="20" t="n">
+      <c r="J178" s="19" t="n">
         <v>8.1</v>
       </c>
-      <c r="K178" s="20" t="n">
+      <c r="K178" s="19" t="n">
         <v>12.7</v>
       </c>
-      <c r="L178" s="20" t="n">
+      <c r="L178" s="19" t="n">
         <v>7.2</v>
       </c>
-      <c r="M178" s="20" t="n">
+      <c r="M178" s="19" t="n">
         <v>3.5</v>
       </c>
-      <c r="N178" s="20" t="n">
+      <c r="N178" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="O178" s="20" t="n">
+      <c r="O178" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="P178" s="20" t="n">
+      <c r="P178" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="Q178" s="20" t="n">
+      <c r="Q178" s="19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="R178" s="44" t="n"/>
-      <c r="S178" s="44" t="n"/>
-      <c r="T178" s="44" t="n"/>
+      <c r="R178" s="37" t="n"/>
+      <c r="S178" s="37" t="n"/>
+      <c r="T178" s="37" t="n"/>
       <c r="U178" t="inlineStr">
         <is>
           <t>Whole Number</t>
@@ -19737,7 +19718,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V181" s="21" t="inlineStr">
+      <c r="V181" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -19798,7 +19779,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V182" s="19" t="inlineStr">
+      <c r="V182" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -19886,7 +19867,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V183" s="21" t="inlineStr">
+      <c r="V183" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -19962,7 +19943,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V184" s="19" t="inlineStr">
+      <c r="V184" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20050,7 +20031,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V185" s="21" t="inlineStr">
+      <c r="V185" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -20122,7 +20103,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V186" s="19" t="inlineStr">
+      <c r="V186" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -20208,7 +20189,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V187" s="21" t="inlineStr">
+      <c r="V187" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -20278,7 +20259,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V188" s="19" t="inlineStr">
+      <c r="V188" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling</t>
         </is>
@@ -20366,7 +20347,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V189" s="21" t="inlineStr">
+      <c r="V189" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20428,7 +20409,7 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="V190" s="19" t="inlineStr">
+      <c r="V190" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20518,7 +20499,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V191" s="21" t="inlineStr">
+      <c r="V191" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20596,7 +20577,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V192" s="19" t="inlineStr">
+      <c r="V192" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20670,7 +20651,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V193" s="21" t="inlineStr">
+      <c r="V193" s="20" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20736,7 +20717,7 @@
           <t>Percentage</t>
         </is>
       </c>
-      <c r="V194" s="19" t="inlineStr">
+      <c r="V194" s="18" t="inlineStr">
         <is>
           <t>Critical Enabling/Leading</t>
         </is>
@@ -20786,8 +20767,8 @@
       <c r="K195" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="L195" s="33" t="n"/>
-      <c r="M195" s="33" t="n"/>
+      <c r="L195" s="29" t="n"/>
+      <c r="M195" s="29" t="n"/>
       <c r="N195" s="2" t="n">
         <v>0.21</v>
       </c>
@@ -20854,8 +20835,8 @@
       <c r="I196" s="2" t="n"/>
       <c r="J196" s="2" t="n"/>
       <c r="K196" s="2" t="n"/>
-      <c r="L196" s="33" t="n"/>
-      <c r="M196" s="33" t="n"/>
+      <c r="L196" s="29" t="n"/>
+      <c r="M196" s="29" t="n"/>
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="2" t="n"/>
       <c r="P196" s="2" t="n"/>

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2624" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2127CEE8-1CB1-498B-BBDD-86A6ABDFFA38}"/>
+  <xr:revisionPtr revIDLastSave="2627" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39B5B639-C97B-4679-B7C2-F0B78AF61D64}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2687,7 +2687,9 @@
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="V6" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="W6" t="s">
         <v>32</v>
       </c>
@@ -17422,11 +17424,6 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -17434,13 +17431,12 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17578,18 +17574,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2637" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9C8203-59B7-4BA8-89DF-033B2D048E51}"/>
+  <xr:revisionPtr revIDLastSave="2638" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9636F25-DCA4-4532-B65C-AE9836CA02C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5913,7 +5913,7 @@
       <c r="P8">
         <v>2</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="17">
         <v>2</v>
       </c>
       <c r="U8" t="s">
@@ -17433,26 +17433,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17590,18 +17570,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2638" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9636F25-DCA4-4532-B65C-AE9836CA02C8}"/>
+  <xr:revisionPtr revIDLastSave="2642" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B505E7-1573-4D12-B60F-7B5504383198}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9132,6 +9132,9 @@
       <c r="P60">
         <v>11</v>
       </c>
+      <c r="Q60">
+        <v>13</v>
+      </c>
       <c r="U60" t="s">
         <v>40</v>
       </c>
@@ -9256,7 +9259,9 @@
       <c r="P62" s="2">
         <v>1</v>
       </c>
-      <c r="Q62" s="2"/>
+      <c r="Q62" s="2">
+        <v>1</v>
+      </c>
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
@@ -9384,7 +9389,9 @@
       <c r="P64" s="2">
         <v>1</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" s="2">
+        <v>1</v>
+      </c>
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
@@ -9512,7 +9519,9 @@
       <c r="P66" s="2">
         <v>1</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" s="2">
+        <v>1</v>
+      </c>
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
@@ -17433,6 +17442,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17570,38 +17599,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2642" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B505E7-1573-4D12-B60F-7B5504383198}"/>
+  <xr:revisionPtr revIDLastSave="2656" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70ED8F49-E0B2-4FCC-999A-ECC4D81F0DCE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1525,7 +1525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1577,6 +1577,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11018,6 +11019,9 @@
       <c r="P91" s="2">
         <v>1</v>
       </c>
+      <c r="Q91" s="2">
+        <v>1</v>
+      </c>
       <c r="V91" s="19" t="s">
         <v>117</v>
       </c>
@@ -11068,6 +11072,12 @@
       <c r="O92" s="12">
         <v>2.5</v>
       </c>
+      <c r="P92" s="2">
+        <v>1.13333333333333</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>0.61111111111111105</v>
+      </c>
       <c r="V92" s="19" t="s">
         <v>117</v>
       </c>
@@ -11118,6 +11128,12 @@
       <c r="O93">
         <v>0</v>
       </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
       <c r="V93" s="19" t="s">
         <v>117</v>
       </c>
@@ -11168,6 +11184,12 @@
       <c r="O94">
         <v>0</v>
       </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
       <c r="V94" s="19" t="s">
         <v>117</v>
       </c>
@@ -11286,8 +11308,12 @@
       <c r="O96">
         <v>100</v>
       </c>
-      <c r="P96" s="8"/>
-      <c r="Q96" s="8"/>
+      <c r="P96" s="49">
+        <v>100</v>
+      </c>
+      <c r="Q96" s="49">
+        <v>100</v>
+      </c>
       <c r="R96" s="8"/>
       <c r="S96" s="8"/>
       <c r="T96" s="8"/>
@@ -17447,21 +17473,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17599,12 +17610,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17612,5 +17638,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -11281,10 +11281,10 @@
         <v>2.5</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>1.13333333333333</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>0.611111111111111</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2657" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BCC1293-016C-4EDB-961D-9CBA5C2A307A}"/>
+  <xr:revisionPtr revIDLastSave="2658" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7395DF7-0255-4BB2-9F31-80671A1278E1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5579,9 +5579,9 @@
   <cols>
     <col min="1" max="5" width="43.42578125" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="11" width="43.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="35.5703125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="7" max="11" width="43.42578125" customWidth="1"/>
+    <col min="12" max="12" width="35.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" customWidth="1"/>
     <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.85546875" customWidth="1"/>
     <col min="16" max="16" width="11.42578125" customWidth="1"/>
@@ -17470,6 +17470,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17607,38 +17627,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2658" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7395DF7-0255-4BB2-9F31-80671A1278E1}"/>
+  <xr:revisionPtr revIDLastSave="2659" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A42A162-746F-45BA-AED8-0C293C658E02}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2405" uniqueCount="319">
   <si>
     <t>Strategic Imperatives</t>
   </si>
@@ -760,9 +760,6 @@
   </si>
   <si>
     <t>Q1 (8%), Q2 (7%) Q3 (6%) Q4 (5%)</t>
-  </si>
-  <si>
-    <t>`</t>
   </si>
   <si>
     <t>Complaint Rate of NPI products Z10</t>
@@ -6297,8 +6294,8 @@
       <c r="O14" s="3">
         <v>0.03</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>131</v>
+      <c r="P14" s="3">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="Q14" s="3">
         <v>3.5000000000000003E-2</v>
@@ -6315,10 +6312,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
         <v>132</v>
-      </c>
-      <c r="B15" t="s">
-        <v>133</v>
       </c>
       <c r="C15" t="s">
         <v>121</v>
@@ -6383,10 +6380,10 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" t="s">
         <v>132</v>
-      </c>
-      <c r="B16" t="s">
-        <v>133</v>
       </c>
       <c r="C16" t="s">
         <v>121</v>
@@ -6445,10 +6442,10 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s">
         <v>134</v>
-      </c>
-      <c r="B17" t="s">
-        <v>135</v>
       </c>
       <c r="C17" t="s">
         <v>121</v>
@@ -6513,10 +6510,10 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" t="s">
         <v>134</v>
-      </c>
-      <c r="B18" t="s">
-        <v>135</v>
       </c>
       <c r="C18" t="s">
         <v>121</v>
@@ -6575,10 +6572,10 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s">
         <v>136</v>
-      </c>
-      <c r="B19" t="s">
-        <v>137</v>
       </c>
       <c r="C19" t="s">
         <v>121</v>
@@ -6643,10 +6640,10 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
         <v>136</v>
-      </c>
-      <c r="B20" t="s">
-        <v>137</v>
       </c>
       <c r="C20" t="s">
         <v>121</v>
@@ -6705,10 +6702,10 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
         <v>138</v>
-      </c>
-      <c r="B21" t="s">
-        <v>139</v>
       </c>
       <c r="C21" t="s">
         <v>121</v>
@@ -6773,10 +6770,10 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" t="s">
         <v>138</v>
-      </c>
-      <c r="B22" t="s">
-        <v>139</v>
       </c>
       <c r="C22" t="s">
         <v>121</v>
@@ -6832,7 +6829,7 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -6905,10 +6902,10 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
         <v>141</v>
-      </c>
-      <c r="B25" t="s">
-        <v>142</v>
       </c>
       <c r="C25" t="s">
         <v>121</v>
@@ -6973,10 +6970,10 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
         <v>141</v>
-      </c>
-      <c r="B26" t="s">
-        <v>142</v>
       </c>
       <c r="C26" t="s">
         <v>121</v>
@@ -7035,10 +7032,10 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
         <v>143</v>
-      </c>
-      <c r="B27" t="s">
-        <v>144</v>
       </c>
       <c r="C27" t="s">
         <v>127</v>
@@ -7103,10 +7100,10 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
         <v>143</v>
-      </c>
-      <c r="B28" t="s">
-        <v>144</v>
       </c>
       <c r="C28" t="s">
         <v>127</v>
@@ -7165,10 +7162,10 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" t="s">
         <v>145</v>
-      </c>
-      <c r="B29" t="s">
-        <v>146</v>
       </c>
       <c r="C29" t="s">
         <v>124</v>
@@ -7233,10 +7230,10 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s">
         <v>145</v>
-      </c>
-      <c r="B30" t="s">
-        <v>146</v>
       </c>
       <c r="C30" t="s">
         <v>124</v>
@@ -7295,10 +7292,10 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s">
         <v>147</v>
-      </c>
-      <c r="B31" t="s">
-        <v>148</v>
       </c>
       <c r="C31" t="s">
         <v>127</v>
@@ -7363,10 +7360,10 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s">
         <v>147</v>
-      </c>
-      <c r="B32" t="s">
-        <v>148</v>
       </c>
       <c r="C32" t="s">
         <v>127</v>
@@ -7425,10 +7422,10 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" t="s">
         <v>149</v>
-      </c>
-      <c r="B33" t="s">
-        <v>150</v>
       </c>
       <c r="C33" t="s">
         <v>127</v>
@@ -7493,10 +7490,10 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" t="s">
         <v>149</v>
-      </c>
-      <c r="B34" t="s">
-        <v>150</v>
       </c>
       <c r="C34" t="s">
         <v>127</v>
@@ -7555,10 +7552,10 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" t="s">
         <v>151</v>
-      </c>
-      <c r="B35" t="s">
-        <v>152</v>
       </c>
       <c r="C35" t="s">
         <v>127</v>
@@ -7599,10 +7596,10 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" t="s">
         <v>151</v>
-      </c>
-      <c r="B36" t="s">
-        <v>152</v>
       </c>
       <c r="C36" t="s">
         <v>127</v>
@@ -7643,10 +7640,10 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" t="s">
         <v>153</v>
-      </c>
-      <c r="B37" t="s">
-        <v>154</v>
       </c>
       <c r="C37" t="s">
         <v>127</v>
@@ -7711,10 +7708,10 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" t="s">
         <v>153</v>
-      </c>
-      <c r="B38" t="s">
-        <v>154</v>
       </c>
       <c r="C38" t="s">
         <v>127</v>
@@ -7773,7 +7770,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V39" s="12"/>
     </row>
@@ -7847,10 +7844,10 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" t="s">
         <v>156</v>
-      </c>
-      <c r="B41" t="s">
-        <v>157</v>
       </c>
       <c r="C41" t="s">
         <v>115</v>
@@ -7915,10 +7912,10 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" t="s">
         <v>156</v>
-      </c>
-      <c r="B42" t="s">
-        <v>157</v>
       </c>
       <c r="C42" t="s">
         <v>115</v>
@@ -7977,16 +7974,16 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s">
         <v>158</v>
-      </c>
-      <c r="B43" t="s">
-        <v>159</v>
       </c>
       <c r="C43" t="s">
         <v>115</v>
       </c>
       <c r="D43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
         <v>39</v>
@@ -8045,16 +8042,16 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" t="s">
         <v>158</v>
-      </c>
-      <c r="B44" t="s">
-        <v>159</v>
       </c>
       <c r="C44" t="s">
         <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
         <v>39</v>
@@ -8104,10 +8101,10 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" t="s">
         <v>161</v>
-      </c>
-      <c r="B45" t="s">
-        <v>162</v>
       </c>
       <c r="C45" t="s">
         <v>115</v>
@@ -8172,10 +8169,10 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" t="s">
         <v>161</v>
-      </c>
-      <c r="B46" t="s">
-        <v>162</v>
       </c>
       <c r="C46" t="s">
         <v>115</v>
@@ -8234,10 +8231,10 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" t="s">
         <v>163</v>
-      </c>
-      <c r="B47" t="s">
-        <v>164</v>
       </c>
       <c r="C47" t="s">
         <v>115</v>
@@ -8285,13 +8282,13 @@
         <v>0.85</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U47" t="s">
         <v>32</v>
@@ -8302,10 +8299,10 @@
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" t="s">
         <v>163</v>
-      </c>
-      <c r="B48" t="s">
-        <v>164</v>
       </c>
       <c r="C48" t="s">
         <v>115</v>
@@ -8353,13 +8350,13 @@
         <v>0.83</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U48" t="s">
         <v>32</v>
@@ -8370,16 +8367,16 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" t="s">
         <v>166</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>167</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>168</v>
-      </c>
-      <c r="D49" t="s">
-        <v>169</v>
       </c>
       <c r="E49" t="s">
         <v>60</v>
@@ -8438,16 +8435,16 @@
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" t="s">
         <v>166</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>167</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>168</v>
-      </c>
-      <c r="D50" t="s">
-        <v>169</v>
       </c>
       <c r="E50" t="s">
         <v>60</v>
@@ -8500,10 +8497,10 @@
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" t="s">
         <v>170</v>
-      </c>
-      <c r="B51" t="s">
-        <v>171</v>
       </c>
       <c r="C51" t="s">
         <v>121</v>
@@ -8568,10 +8565,10 @@
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B52" t="s">
         <v>170</v>
-      </c>
-      <c r="B52" t="s">
-        <v>171</v>
       </c>
       <c r="C52" t="s">
         <v>121</v>
@@ -8630,16 +8627,16 @@
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" t="s">
         <v>172</v>
-      </c>
-      <c r="B53" t="s">
-        <v>173</v>
       </c>
       <c r="C53" t="s">
         <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
         <v>60</v>
@@ -8698,16 +8695,16 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" t="s">
         <v>172</v>
-      </c>
-      <c r="B54" t="s">
-        <v>173</v>
       </c>
       <c r="C54" t="s">
         <v>115</v>
       </c>
       <c r="D54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
         <v>60</v>
@@ -8760,10 +8757,10 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" t="s">
         <v>175</v>
-      </c>
-      <c r="B55" t="s">
-        <v>176</v>
       </c>
       <c r="C55" t="s">
         <v>115</v>
@@ -8828,10 +8825,10 @@
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56" t="s">
         <v>175</v>
-      </c>
-      <c r="B56" t="s">
-        <v>176</v>
       </c>
       <c r="C56" t="s">
         <v>115</v>
@@ -8890,16 +8887,16 @@
     </row>
     <row r="57" spans="1:22">
       <c r="A57" t="s">
+        <v>176</v>
+      </c>
+      <c r="B57" t="s">
         <v>177</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>167</v>
+      </c>
+      <c r="D57" t="s">
         <v>178</v>
-      </c>
-      <c r="C57" t="s">
-        <v>168</v>
-      </c>
-      <c r="D57" t="s">
-        <v>179</v>
       </c>
       <c r="E57" t="s">
         <v>29</v>
@@ -8958,16 +8955,16 @@
     </row>
     <row r="58" spans="1:22">
       <c r="A58" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" t="s">
         <v>177</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>167</v>
+      </c>
+      <c r="D58" t="s">
         <v>178</v>
-      </c>
-      <c r="C58" t="s">
-        <v>168</v>
-      </c>
-      <c r="D58" t="s">
-        <v>179</v>
       </c>
       <c r="E58" t="s">
         <v>29</v>
@@ -9020,10 +9017,10 @@
     </row>
     <row r="59" spans="1:22">
       <c r="A59" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" t="s">
         <v>180</v>
-      </c>
-      <c r="B59" t="s">
-        <v>181</v>
       </c>
       <c r="C59" t="s">
         <v>127</v>
@@ -9041,7 +9038,7 @@
         <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I59" s="17">
         <v>15</v>
@@ -9088,10 +9085,10 @@
     </row>
     <row r="60" spans="1:22">
       <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
         <v>180</v>
-      </c>
-      <c r="B60" t="s">
-        <v>181</v>
       </c>
       <c r="C60" t="s">
         <v>127</v>
@@ -9147,10 +9144,10 @@
     </row>
     <row r="61" spans="1:22">
       <c r="A61" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" t="s">
         <v>183</v>
-      </c>
-      <c r="B61" t="s">
-        <v>184</v>
       </c>
       <c r="C61" t="s">
         <v>127</v>
@@ -9215,10 +9212,10 @@
     </row>
     <row r="62" spans="1:22">
       <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
         <v>183</v>
-      </c>
-      <c r="B62" t="s">
-        <v>184</v>
       </c>
       <c r="C62" t="s">
         <v>127</v>
@@ -9277,10 +9274,10 @@
     </row>
     <row r="63" spans="1:22">
       <c r="A63" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" t="s">
         <v>185</v>
-      </c>
-      <c r="B63" t="s">
-        <v>186</v>
       </c>
       <c r="C63" t="s">
         <v>127</v>
@@ -9345,10 +9342,10 @@
     </row>
     <row r="64" spans="1:22">
       <c r="A64" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" t="s">
         <v>185</v>
-      </c>
-      <c r="B64" t="s">
-        <v>186</v>
       </c>
       <c r="C64" t="s">
         <v>127</v>
@@ -9407,10 +9404,10 @@
     </row>
     <row r="65" spans="1:22">
       <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" t="s">
         <v>187</v>
-      </c>
-      <c r="B65" t="s">
-        <v>188</v>
       </c>
       <c r="C65" t="s">
         <v>127</v>
@@ -9475,10 +9472,10 @@
     </row>
     <row r="66" spans="1:22">
       <c r="A66" t="s">
+        <v>186</v>
+      </c>
+      <c r="B66" t="s">
         <v>187</v>
-      </c>
-      <c r="B66" t="s">
-        <v>188</v>
       </c>
       <c r="C66" t="s">
         <v>127</v>
@@ -9537,13 +9534,13 @@
     </row>
     <row r="67" spans="1:22" ht="14.1" customHeight="1">
       <c r="A67" t="s">
+        <v>188</v>
+      </c>
+      <c r="B67" t="s">
         <v>189</v>
       </c>
-      <c r="B67" t="s">
-        <v>190</v>
-      </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D67">
         <v>0.03</v>
@@ -9596,13 +9593,13 @@
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
+        <v>188</v>
+      </c>
+      <c r="B68" t="s">
         <v>189</v>
       </c>
-      <c r="B68" t="s">
-        <v>190</v>
-      </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D68">
         <v>0.03</v>
@@ -9655,10 +9652,10 @@
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
+        <v>190</v>
+      </c>
+      <c r="B69" t="s">
         <v>191</v>
-      </c>
-      <c r="B69" t="s">
-        <v>192</v>
       </c>
       <c r="C69" t="s">
         <v>127</v>
@@ -9723,10 +9720,10 @@
     </row>
     <row r="70" spans="1:22">
       <c r="A70" t="s">
+        <v>190</v>
+      </c>
+      <c r="B70" t="s">
         <v>191</v>
-      </c>
-      <c r="B70" t="s">
-        <v>192</v>
       </c>
       <c r="C70" t="s">
         <v>127</v>
@@ -9785,10 +9782,10 @@
     </row>
     <row r="71" spans="1:22">
       <c r="A71" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" t="s">
         <v>193</v>
-      </c>
-      <c r="B71" t="s">
-        <v>194</v>
       </c>
       <c r="C71" t="s">
         <v>121</v>
@@ -9853,10 +9850,10 @@
     </row>
     <row r="72" spans="1:22">
       <c r="A72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" t="s">
         <v>193</v>
-      </c>
-      <c r="B72" t="s">
-        <v>194</v>
       </c>
       <c r="C72" t="s">
         <v>121</v>
@@ -9912,10 +9909,10 @@
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
+        <v>194</v>
+      </c>
+      <c r="B73" t="s">
         <v>195</v>
-      </c>
-      <c r="B73" t="s">
-        <v>196</v>
       </c>
       <c r="C73" t="s">
         <v>121</v>
@@ -9980,10 +9977,10 @@
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" t="s">
         <v>195</v>
-      </c>
-      <c r="B74" t="s">
-        <v>196</v>
       </c>
       <c r="C74" t="s">
         <v>121</v>
@@ -10027,10 +10024,10 @@
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C75" t="s">
         <v>121</v>
@@ -10095,10 +10092,10 @@
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C76" t="s">
         <v>121</v>
@@ -10157,16 +10154,16 @@
     </row>
     <row r="77" spans="1:22">
       <c r="A77" t="s">
+        <v>197</v>
+      </c>
+      <c r="B77" t="s">
         <v>198</v>
-      </c>
-      <c r="B77" t="s">
-        <v>199</v>
       </c>
       <c r="C77" t="s">
         <v>121</v>
       </c>
       <c r="D77" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
@@ -10225,16 +10222,16 @@
     </row>
     <row r="78" spans="1:22">
       <c r="A78" t="s">
+        <v>197</v>
+      </c>
+      <c r="B78" t="s">
         <v>198</v>
-      </c>
-      <c r="B78" t="s">
-        <v>199</v>
       </c>
       <c r="C78" t="s">
         <v>121</v>
       </c>
       <c r="D78" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E78" t="s">
         <v>29</v>
@@ -10284,10 +10281,10 @@
     </row>
     <row r="79" spans="1:22">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C79" t="s">
         <v>127</v>
@@ -10352,10 +10349,10 @@
     </row>
     <row r="80" spans="1:22">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B80" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C80" t="s">
         <v>127</v>
@@ -10414,10 +10411,10 @@
     </row>
     <row r="81" spans="1:22">
       <c r="A81" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" t="s">
         <v>202</v>
-      </c>
-      <c r="B81" t="s">
-        <v>203</v>
       </c>
       <c r="C81" t="s">
         <v>124</v>
@@ -10482,10 +10479,10 @@
     </row>
     <row r="82" spans="1:22">
       <c r="A82" t="s">
+        <v>201</v>
+      </c>
+      <c r="B82" t="s">
         <v>202</v>
-      </c>
-      <c r="B82" t="s">
-        <v>203</v>
       </c>
       <c r="C82" t="s">
         <v>124</v>
@@ -10532,7 +10529,7 @@
     </row>
     <row r="83" spans="1:22">
       <c r="A83" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -10605,10 +10602,10 @@
     </row>
     <row r="85" spans="1:22" ht="72.75">
       <c r="A85" t="s">
+        <v>204</v>
+      </c>
+      <c r="B85" s="43" t="s">
         <v>205</v>
-      </c>
-      <c r="B85" s="43" t="s">
-        <v>206</v>
       </c>
       <c r="C85" t="s">
         <v>127</v>
@@ -10673,10 +10670,10 @@
     </row>
     <row r="86" spans="1:22" ht="72.75">
       <c r="A86" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="43" t="s">
         <v>205</v>
-      </c>
-      <c r="B86" s="43" t="s">
-        <v>206</v>
       </c>
       <c r="C86" t="s">
         <v>127</v>
@@ -10732,10 +10729,10 @@
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
+        <v>206</v>
+      </c>
+      <c r="B87" t="s">
         <v>207</v>
-      </c>
-      <c r="B87" t="s">
-        <v>208</v>
       </c>
       <c r="C87" t="s">
         <v>127</v>
@@ -10800,10 +10797,10 @@
     </row>
     <row r="88" spans="1:22">
       <c r="A88" t="s">
+        <v>206</v>
+      </c>
+      <c r="B88" t="s">
         <v>207</v>
-      </c>
-      <c r="B88" t="s">
-        <v>208</v>
       </c>
       <c r="C88" t="s">
         <v>127</v>
@@ -10859,10 +10856,10 @@
     </row>
     <row r="89" spans="1:22">
       <c r="A89" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" t="s">
         <v>209</v>
-      </c>
-      <c r="B89" t="s">
-        <v>210</v>
       </c>
       <c r="C89" t="s">
         <v>127</v>
@@ -10918,10 +10915,10 @@
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
+        <v>208</v>
+      </c>
+      <c r="B90" t="s">
         <v>209</v>
-      </c>
-      <c r="B90" t="s">
-        <v>210</v>
       </c>
       <c r="C90" t="s">
         <v>127</v>
@@ -10974,16 +10971,16 @@
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
+        <v>210</v>
+      </c>
+      <c r="B91" t="s">
         <v>211</v>
-      </c>
-      <c r="B91" t="s">
-        <v>212</v>
       </c>
       <c r="C91" t="s">
         <v>127</v>
       </c>
       <c r="D91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E91" t="s">
         <v>29</v>
@@ -11030,16 +11027,16 @@
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
+        <v>210</v>
+      </c>
+      <c r="B92" t="s">
         <v>211</v>
-      </c>
-      <c r="B92" t="s">
-        <v>212</v>
       </c>
       <c r="C92" t="s">
         <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E92" t="s">
         <v>29</v>
@@ -11086,10 +11083,10 @@
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
+        <v>213</v>
+      </c>
+      <c r="B93" t="s">
         <v>214</v>
-      </c>
-      <c r="B93" t="s">
-        <v>215</v>
       </c>
       <c r="C93" t="s">
         <v>127</v>
@@ -11142,10 +11139,10 @@
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
+        <v>213</v>
+      </c>
+      <c r="B94" t="s">
         <v>214</v>
-      </c>
-      <c r="B94" t="s">
-        <v>215</v>
       </c>
       <c r="C94" t="s">
         <v>127</v>
@@ -11198,10 +11195,10 @@
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
+        <v>215</v>
+      </c>
+      <c r="B95" t="s">
         <v>216</v>
-      </c>
-      <c r="B95" t="s">
-        <v>217</v>
       </c>
       <c r="C95" t="s">
         <v>127</v>
@@ -11266,10 +11263,10 @@
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" t="s">
         <v>216</v>
-      </c>
-      <c r="B96" t="s">
-        <v>217</v>
       </c>
       <c r="C96" t="s">
         <v>127</v>
@@ -11328,10 +11325,10 @@
     </row>
     <row r="97" spans="1:22">
       <c r="A97" t="s">
+        <v>217</v>
+      </c>
+      <c r="B97" t="s">
         <v>218</v>
-      </c>
-      <c r="B97" t="s">
-        <v>219</v>
       </c>
       <c r="C97" t="s">
         <v>127</v>
@@ -11396,10 +11393,10 @@
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" t="s">
         <v>218</v>
-      </c>
-      <c r="B98" t="s">
-        <v>219</v>
       </c>
       <c r="C98" t="s">
         <v>127</v>
@@ -11455,10 +11452,10 @@
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" t="s">
         <v>220</v>
-      </c>
-      <c r="B99" t="s">
-        <v>221</v>
       </c>
       <c r="C99" t="s">
         <v>127</v>
@@ -11523,10 +11520,10 @@
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" t="s">
         <v>220</v>
-      </c>
-      <c r="B100" t="s">
-        <v>221</v>
       </c>
       <c r="C100" t="s">
         <v>127</v>
@@ -11585,7 +11582,7 @@
         <v>76</v>
       </c>
       <c r="B101" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C101" t="s">
         <v>127</v>
@@ -11653,7 +11650,7 @@
         <v>76</v>
       </c>
       <c r="B102" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C102" t="s">
         <v>127</v>
@@ -11709,7 +11706,7 @@
     </row>
     <row r="103" spans="1:22">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:22">
@@ -11782,10 +11779,10 @@
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
+        <v>223</v>
+      </c>
+      <c r="B105" t="s">
         <v>224</v>
-      </c>
-      <c r="B105" t="s">
-        <v>225</v>
       </c>
       <c r="C105" t="s">
         <v>127</v>
@@ -11850,10 +11847,10 @@
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
+        <v>223</v>
+      </c>
+      <c r="B106" t="s">
         <v>224</v>
-      </c>
-      <c r="B106" t="s">
-        <v>225</v>
       </c>
       <c r="C106" t="s">
         <v>127</v>
@@ -11912,10 +11909,10 @@
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
+        <v>225</v>
+      </c>
+      <c r="B107" t="s">
         <v>226</v>
-      </c>
-      <c r="B107" t="s">
-        <v>227</v>
       </c>
       <c r="C107" t="s">
         <v>127</v>
@@ -11980,10 +11977,10 @@
     </row>
     <row r="108" spans="1:22">
       <c r="A108" t="s">
+        <v>225</v>
+      </c>
+      <c r="B108" t="s">
         <v>226</v>
-      </c>
-      <c r="B108" t="s">
-        <v>227</v>
       </c>
       <c r="C108" t="s">
         <v>127</v>
@@ -12039,10 +12036,10 @@
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
+        <v>227</v>
+      </c>
+      <c r="B109" t="s">
         <v>228</v>
-      </c>
-      <c r="B109" t="s">
-        <v>229</v>
       </c>
       <c r="C109" t="s">
         <v>127</v>
@@ -12107,10 +12104,10 @@
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
+        <v>227</v>
+      </c>
+      <c r="B110" t="s">
         <v>228</v>
-      </c>
-      <c r="B110" t="s">
-        <v>229</v>
       </c>
       <c r="C110" t="s">
         <v>127</v>
@@ -12166,10 +12163,10 @@
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
+        <v>229</v>
+      </c>
+      <c r="B111" t="s">
         <v>230</v>
-      </c>
-      <c r="B111" t="s">
-        <v>231</v>
       </c>
       <c r="C111" t="s">
         <v>127</v>
@@ -12234,10 +12231,10 @@
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
+        <v>229</v>
+      </c>
+      <c r="B112" t="s">
         <v>230</v>
-      </c>
-      <c r="B112" t="s">
-        <v>231</v>
       </c>
       <c r="C112" t="s">
         <v>127</v>
@@ -12296,10 +12293,10 @@
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
+        <v>231</v>
+      </c>
+      <c r="B113" t="s">
         <v>232</v>
-      </c>
-      <c r="B113" t="s">
-        <v>233</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
@@ -12364,10 +12361,10 @@
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
+        <v>231</v>
+      </c>
+      <c r="B114" t="s">
         <v>232</v>
-      </c>
-      <c r="B114" t="s">
-        <v>233</v>
       </c>
       <c r="C114" t="s">
         <v>127</v>
@@ -12422,10 +12419,10 @@
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
+        <v>233</v>
+      </c>
+      <c r="B115" t="s">
         <v>234</v>
-      </c>
-      <c r="B115" t="s">
-        <v>235</v>
       </c>
       <c r="C115" t="s">
         <v>127</v>
@@ -12486,10 +12483,10 @@
     </row>
     <row r="116" spans="1:22">
       <c r="A116" t="s">
+        <v>233</v>
+      </c>
+      <c r="B116" t="s">
         <v>234</v>
-      </c>
-      <c r="B116" t="s">
-        <v>235</v>
       </c>
       <c r="C116" t="s">
         <v>127</v>
@@ -12544,7 +12541,7 @@
     </row>
     <row r="117" spans="1:22">
       <c r="A117" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="118" spans="1:22">
@@ -12617,10 +12614,10 @@
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" t="s">
         <v>237</v>
-      </c>
-      <c r="B119" t="s">
-        <v>238</v>
       </c>
       <c r="C119" t="s">
         <v>127</v>
@@ -12685,10 +12682,10 @@
     </row>
     <row r="120" spans="1:22">
       <c r="A120" t="s">
+        <v>236</v>
+      </c>
+      <c r="B120" t="s">
         <v>237</v>
-      </c>
-      <c r="B120" t="s">
-        <v>238</v>
       </c>
       <c r="C120" t="s">
         <v>127</v>
@@ -12747,10 +12744,10 @@
     </row>
     <row r="121" spans="1:22">
       <c r="A121" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" t="s">
         <v>239</v>
-      </c>
-      <c r="B121" t="s">
-        <v>240</v>
       </c>
       <c r="C121" t="s">
         <v>127</v>
@@ -12815,10 +12812,10 @@
     </row>
     <row r="122" spans="1:22">
       <c r="A122" t="s">
+        <v>238</v>
+      </c>
+      <c r="B122" t="s">
         <v>239</v>
-      </c>
-      <c r="B122" t="s">
-        <v>240</v>
       </c>
       <c r="C122" t="s">
         <v>127</v>
@@ -12877,10 +12874,10 @@
     </row>
     <row r="123" spans="1:22">
       <c r="A123" t="s">
+        <v>240</v>
+      </c>
+      <c r="B123" t="s">
         <v>241</v>
-      </c>
-      <c r="B123" t="s">
-        <v>242</v>
       </c>
       <c r="C123" t="s">
         <v>127</v>
@@ -12945,10 +12942,10 @@
     </row>
     <row r="124" spans="1:22">
       <c r="A124" t="s">
+        <v>240</v>
+      </c>
+      <c r="B124" t="s">
         <v>241</v>
-      </c>
-      <c r="B124" t="s">
-        <v>242</v>
       </c>
       <c r="C124" t="s">
         <v>127</v>
@@ -13004,10 +13001,10 @@
     </row>
     <row r="125" spans="1:22">
       <c r="A125" t="s">
+        <v>242</v>
+      </c>
+      <c r="B125" t="s">
         <v>243</v>
-      </c>
-      <c r="B125" t="s">
-        <v>244</v>
       </c>
       <c r="C125" t="s">
         <v>121</v>
@@ -13072,10 +13069,10 @@
     </row>
     <row r="126" spans="1:22">
       <c r="A126" t="s">
+        <v>242</v>
+      </c>
+      <c r="B126" t="s">
         <v>243</v>
-      </c>
-      <c r="B126" t="s">
-        <v>244</v>
       </c>
       <c r="C126" t="s">
         <v>121</v>
@@ -13131,10 +13128,10 @@
     </row>
     <row r="127" spans="1:22">
       <c r="A127" t="s">
+        <v>244</v>
+      </c>
+      <c r="B127" t="s">
         <v>245</v>
-      </c>
-      <c r="B127" t="s">
-        <v>246</v>
       </c>
       <c r="C127" t="s">
         <v>127</v>
@@ -13199,10 +13196,10 @@
     </row>
     <row r="128" spans="1:22">
       <c r="A128" t="s">
+        <v>244</v>
+      </c>
+      <c r="B128" t="s">
         <v>245</v>
-      </c>
-      <c r="B128" t="s">
-        <v>246</v>
       </c>
       <c r="C128" t="s">
         <v>127</v>
@@ -13261,10 +13258,10 @@
     </row>
     <row r="129" spans="1:22">
       <c r="A129" t="s">
+        <v>246</v>
+      </c>
+      <c r="B129" t="s">
         <v>247</v>
-      </c>
-      <c r="B129" t="s">
-        <v>248</v>
       </c>
       <c r="C129" t="s">
         <v>127</v>
@@ -13329,10 +13326,10 @@
     </row>
     <row r="130" spans="1:22">
       <c r="A130" t="s">
+        <v>246</v>
+      </c>
+      <c r="B130" t="s">
         <v>247</v>
-      </c>
-      <c r="B130" t="s">
-        <v>248</v>
       </c>
       <c r="C130" t="s">
         <v>127</v>
@@ -13391,10 +13388,10 @@
     </row>
     <row r="131" spans="1:22">
       <c r="A131" t="s">
+        <v>248</v>
+      </c>
+      <c r="B131" t="s">
         <v>249</v>
-      </c>
-      <c r="B131" t="s">
-        <v>250</v>
       </c>
       <c r="C131" t="s">
         <v>121</v>
@@ -13459,10 +13456,10 @@
     </row>
     <row r="132" spans="1:22">
       <c r="A132" t="s">
+        <v>248</v>
+      </c>
+      <c r="B132" t="s">
         <v>249</v>
-      </c>
-      <c r="B132" t="s">
-        <v>250</v>
       </c>
       <c r="C132" t="s">
         <v>121</v>
@@ -13521,10 +13518,10 @@
     </row>
     <row r="133" spans="1:22">
       <c r="A133" t="s">
+        <v>250</v>
+      </c>
+      <c r="B133" t="s">
         <v>251</v>
-      </c>
-      <c r="B133" t="s">
-        <v>252</v>
       </c>
       <c r="C133" t="s">
         <v>127</v>
@@ -13573,10 +13570,10 @@
     </row>
     <row r="134" spans="1:22">
       <c r="A134" t="s">
+        <v>250</v>
+      </c>
+      <c r="B134" t="s">
         <v>251</v>
-      </c>
-      <c r="B134" t="s">
-        <v>252</v>
       </c>
       <c r="C134" t="s">
         <v>127</v>
@@ -13623,10 +13620,10 @@
     </row>
     <row r="135" spans="1:22">
       <c r="A135" t="s">
+        <v>252</v>
+      </c>
+      <c r="B135" t="s">
         <v>253</v>
-      </c>
-      <c r="B135" t="s">
-        <v>254</v>
       </c>
       <c r="C135" t="s">
         <v>127</v>
@@ -13685,10 +13682,10 @@
     </row>
     <row r="136" spans="1:22">
       <c r="A136" t="s">
+        <v>252</v>
+      </c>
+      <c r="B136" t="s">
         <v>253</v>
-      </c>
-      <c r="B136" t="s">
-        <v>254</v>
       </c>
       <c r="C136" t="s">
         <v>127</v>
@@ -13747,10 +13744,10 @@
     </row>
     <row r="137" spans="1:22">
       <c r="A137" t="s">
+        <v>254</v>
+      </c>
+      <c r="B137" t="s">
         <v>255</v>
-      </c>
-      <c r="B137" t="s">
-        <v>256</v>
       </c>
       <c r="C137" t="s">
         <v>127</v>
@@ -13815,10 +13812,10 @@
     </row>
     <row r="138" spans="1:22">
       <c r="A138" t="s">
+        <v>254</v>
+      </c>
+      <c r="B138" t="s">
         <v>255</v>
-      </c>
-      <c r="B138" t="s">
-        <v>256</v>
       </c>
       <c r="C138" t="s">
         <v>127</v>
@@ -13877,7 +13874,7 @@
     </row>
     <row r="139" spans="1:22">
       <c r="A139" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="140" spans="1:22">
@@ -13950,16 +13947,16 @@
     </row>
     <row r="141" spans="1:22">
       <c r="A141" t="s">
+        <v>257</v>
+      </c>
+      <c r="B141" t="s">
         <v>258</v>
-      </c>
-      <c r="B141" t="s">
-        <v>259</v>
       </c>
       <c r="C141" t="s">
         <v>127</v>
       </c>
       <c r="D141" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E141" t="s">
         <v>39</v>
@@ -14018,16 +14015,16 @@
     </row>
     <row r="142" spans="1:22">
       <c r="A142" t="s">
+        <v>257</v>
+      </c>
+      <c r="B142" t="s">
         <v>258</v>
-      </c>
-      <c r="B142" t="s">
-        <v>259</v>
       </c>
       <c r="C142" t="s">
         <v>127</v>
       </c>
       <c r="D142" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E142" t="s">
         <v>39</v>
@@ -14074,10 +14071,10 @@
     </row>
     <row r="143" spans="1:22">
       <c r="A143" t="s">
+        <v>260</v>
+      </c>
+      <c r="B143" t="s">
         <v>261</v>
-      </c>
-      <c r="B143" t="s">
-        <v>262</v>
       </c>
       <c r="C143" t="s">
         <v>127</v>
@@ -14142,10 +14139,10 @@
     </row>
     <row r="144" spans="1:22">
       <c r="A144" t="s">
+        <v>260</v>
+      </c>
+      <c r="B144" t="s">
         <v>261</v>
-      </c>
-      <c r="B144" t="s">
-        <v>262</v>
       </c>
       <c r="C144" t="s">
         <v>127</v>
@@ -14195,10 +14192,10 @@
     </row>
     <row r="145" spans="1:22">
       <c r="A145" t="s">
+        <v>262</v>
+      </c>
+      <c r="B145" t="s">
         <v>263</v>
-      </c>
-      <c r="B145" t="s">
-        <v>264</v>
       </c>
       <c r="C145" t="s">
         <v>127</v>
@@ -14263,10 +14260,10 @@
     </row>
     <row r="146" spans="1:22">
       <c r="A146" t="s">
+        <v>262</v>
+      </c>
+      <c r="B146" t="s">
         <v>263</v>
-      </c>
-      <c r="B146" t="s">
-        <v>264</v>
       </c>
       <c r="C146" t="s">
         <v>127</v>
@@ -14321,10 +14318,10 @@
     </row>
     <row r="147" spans="1:22">
       <c r="A147" t="s">
+        <v>264</v>
+      </c>
+      <c r="B147" t="s">
         <v>265</v>
-      </c>
-      <c r="B147" t="s">
-        <v>266</v>
       </c>
       <c r="C147" t="s">
         <v>127</v>
@@ -14389,10 +14386,10 @@
     </row>
     <row r="148" spans="1:22">
       <c r="A148" t="s">
+        <v>264</v>
+      </c>
+      <c r="B148" t="s">
         <v>265</v>
-      </c>
-      <c r="B148" t="s">
-        <v>266</v>
       </c>
       <c r="C148" t="s">
         <v>127</v>
@@ -14439,10 +14436,10 @@
     </row>
     <row r="149" spans="1:22">
       <c r="A149" t="s">
+        <v>266</v>
+      </c>
+      <c r="B149" t="s">
         <v>267</v>
-      </c>
-      <c r="B149" t="s">
-        <v>268</v>
       </c>
       <c r="C149" t="s">
         <v>127</v>
@@ -14507,10 +14504,10 @@
     </row>
     <row r="150" spans="1:22">
       <c r="A150" t="s">
+        <v>266</v>
+      </c>
+      <c r="B150" t="s">
         <v>267</v>
-      </c>
-      <c r="B150" t="s">
-        <v>268</v>
       </c>
       <c r="C150" t="s">
         <v>127</v>
@@ -14565,10 +14562,10 @@
     </row>
     <row r="151" spans="1:22">
       <c r="A151" t="s">
+        <v>268</v>
+      </c>
+      <c r="B151" t="s">
         <v>269</v>
-      </c>
-      <c r="B151" t="s">
-        <v>270</v>
       </c>
       <c r="C151" t="s">
         <v>127</v>
@@ -14633,10 +14630,10 @@
     </row>
     <row r="152" spans="1:22">
       <c r="A152" t="s">
+        <v>268</v>
+      </c>
+      <c r="B152" t="s">
         <v>269</v>
-      </c>
-      <c r="B152" t="s">
-        <v>270</v>
       </c>
       <c r="C152" t="s">
         <v>127</v>
@@ -14691,10 +14688,10 @@
     </row>
     <row r="153" spans="1:22">
       <c r="A153" t="s">
+        <v>270</v>
+      </c>
+      <c r="B153" t="s">
         <v>271</v>
-      </c>
-      <c r="B153" t="s">
-        <v>272</v>
       </c>
       <c r="C153" t="s">
         <v>124</v>
@@ -14759,10 +14756,10 @@
     </row>
     <row r="154" spans="1:22">
       <c r="A154" t="s">
+        <v>270</v>
+      </c>
+      <c r="B154" t="s">
         <v>271</v>
-      </c>
-      <c r="B154" t="s">
-        <v>272</v>
       </c>
       <c r="C154" t="s">
         <v>124</v>
@@ -14809,16 +14806,16 @@
     </row>
     <row r="155" spans="1:22">
       <c r="A155" t="s">
+        <v>272</v>
+      </c>
+      <c r="B155" t="s">
         <v>273</v>
-      </c>
-      <c r="B155" t="s">
-        <v>274</v>
       </c>
       <c r="C155" t="s">
         <v>115</v>
       </c>
       <c r="D155" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E155" t="s">
         <v>60</v>
@@ -14877,16 +14874,16 @@
     </row>
     <row r="156" spans="1:22">
       <c r="A156" t="s">
+        <v>272</v>
+      </c>
+      <c r="B156" t="s">
         <v>273</v>
-      </c>
-      <c r="B156" t="s">
-        <v>274</v>
       </c>
       <c r="C156" t="s">
         <v>115</v>
       </c>
       <c r="D156" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E156" t="s">
         <v>60</v>
@@ -14935,10 +14932,10 @@
     </row>
     <row r="157" spans="1:22">
       <c r="A157" t="s">
+        <v>275</v>
+      </c>
+      <c r="B157" t="s">
         <v>276</v>
-      </c>
-      <c r="B157" t="s">
-        <v>277</v>
       </c>
       <c r="C157" t="s">
         <v>127</v>
@@ -15003,10 +15000,10 @@
     </row>
     <row r="158" spans="1:22">
       <c r="A158" t="s">
+        <v>275</v>
+      </c>
+      <c r="B158" t="s">
         <v>276</v>
-      </c>
-      <c r="B158" t="s">
-        <v>277</v>
       </c>
       <c r="C158" t="s">
         <v>127</v>
@@ -15057,7 +15054,7 @@
     </row>
     <row r="159" spans="1:22">
       <c r="A159" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:22">
@@ -15130,10 +15127,10 @@
     </row>
     <row r="161" spans="1:22">
       <c r="A161" t="s">
+        <v>278</v>
+      </c>
+      <c r="B161" t="s">
         <v>279</v>
-      </c>
-      <c r="B161" t="s">
-        <v>280</v>
       </c>
       <c r="C161" t="s">
         <v>124</v>
@@ -15198,10 +15195,10 @@
     </row>
     <row r="162" spans="1:22">
       <c r="A162" t="s">
+        <v>278</v>
+      </c>
+      <c r="B162" t="s">
         <v>279</v>
-      </c>
-      <c r="B162" t="s">
-        <v>280</v>
       </c>
       <c r="C162" t="s">
         <v>124</v>
@@ -15256,10 +15253,10 @@
     </row>
     <row r="163" spans="1:22">
       <c r="A163" t="s">
+        <v>280</v>
+      </c>
+      <c r="B163" t="s">
         <v>281</v>
-      </c>
-      <c r="B163" t="s">
-        <v>282</v>
       </c>
       <c r="C163" t="s">
         <v>124</v>
@@ -15324,10 +15321,10 @@
     </row>
     <row r="164" spans="1:22">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
       <c r="C164" t="s">
         <v>124</v>
@@ -15386,10 +15383,10 @@
     </row>
     <row r="165" spans="1:22">
       <c r="A165" t="s">
+        <v>282</v>
+      </c>
+      <c r="B165" t="s">
         <v>283</v>
-      </c>
-      <c r="B165" t="s">
-        <v>284</v>
       </c>
       <c r="C165" t="s">
         <v>124</v>
@@ -15454,10 +15451,10 @@
     </row>
     <row r="166" spans="1:22">
       <c r="A166" t="s">
+        <v>282</v>
+      </c>
+      <c r="B166" t="s">
         <v>283</v>
-      </c>
-      <c r="B166" t="s">
-        <v>284</v>
       </c>
       <c r="C166" t="s">
         <v>124</v>
@@ -15514,10 +15511,10 @@
     </row>
     <row r="167" spans="1:22">
       <c r="A167" t="s">
+        <v>284</v>
+      </c>
+      <c r="B167" t="s">
         <v>285</v>
-      </c>
-      <c r="B167" t="s">
-        <v>286</v>
       </c>
       <c r="C167" t="s">
         <v>124</v>
@@ -15582,10 +15579,10 @@
     </row>
     <row r="168" spans="1:22">
       <c r="A168" t="s">
+        <v>284</v>
+      </c>
+      <c r="B168" t="s">
         <v>285</v>
-      </c>
-      <c r="B168" t="s">
-        <v>286</v>
       </c>
       <c r="C168" t="s">
         <v>124</v>
@@ -15640,10 +15637,10 @@
     </row>
     <row r="169" spans="1:22">
       <c r="A169" t="s">
+        <v>286</v>
+      </c>
+      <c r="B169" t="s">
         <v>287</v>
-      </c>
-      <c r="B169" t="s">
-        <v>288</v>
       </c>
       <c r="C169" t="s">
         <v>127</v>
@@ -15708,10 +15705,10 @@
     </row>
     <row r="170" spans="1:22">
       <c r="A170" t="s">
+        <v>286</v>
+      </c>
+      <c r="B170" t="s">
         <v>287</v>
-      </c>
-      <c r="B170" t="s">
-        <v>288</v>
       </c>
       <c r="C170" t="s">
         <v>127</v>
@@ -15768,10 +15765,10 @@
     </row>
     <row r="171" spans="1:22">
       <c r="A171" t="s">
+        <v>288</v>
+      </c>
+      <c r="B171" t="s">
         <v>289</v>
-      </c>
-      <c r="B171" t="s">
-        <v>290</v>
       </c>
       <c r="C171" t="s">
         <v>124</v>
@@ -15814,10 +15811,10 @@
     </row>
     <row r="172" spans="1:22">
       <c r="A172" t="s">
+        <v>288</v>
+      </c>
+      <c r="B172" t="s">
         <v>289</v>
-      </c>
-      <c r="B172" t="s">
-        <v>290</v>
       </c>
       <c r="C172" t="s">
         <v>124</v>
@@ -15862,10 +15859,10 @@
     </row>
     <row r="173" spans="1:22">
       <c r="A173" t="s">
+        <v>290</v>
+      </c>
+      <c r="B173" t="s">
         <v>291</v>
-      </c>
-      <c r="B173" t="s">
-        <v>292</v>
       </c>
       <c r="C173" t="s">
         <v>124</v>
@@ -15930,10 +15927,10 @@
     </row>
     <row r="174" spans="1:22">
       <c r="A174" t="s">
+        <v>290</v>
+      </c>
+      <c r="B174" t="s">
         <v>291</v>
-      </c>
-      <c r="B174" t="s">
-        <v>292</v>
       </c>
       <c r="C174" t="s">
         <v>124</v>
@@ -15990,10 +15987,10 @@
     </row>
     <row r="175" spans="1:22">
       <c r="A175" t="s">
+        <v>292</v>
+      </c>
+      <c r="B175" t="s">
         <v>293</v>
-      </c>
-      <c r="B175" t="s">
-        <v>294</v>
       </c>
       <c r="C175" t="s">
         <v>124</v>
@@ -16058,10 +16055,10 @@
     </row>
     <row r="176" spans="1:22">
       <c r="A176" t="s">
+        <v>292</v>
+      </c>
+      <c r="B176" t="s">
         <v>293</v>
-      </c>
-      <c r="B176" t="s">
-        <v>294</v>
       </c>
       <c r="C176" t="s">
         <v>124</v>
@@ -16118,10 +16115,10 @@
     </row>
     <row r="177" spans="1:22">
       <c r="A177" t="s">
+        <v>294</v>
+      </c>
+      <c r="B177" t="s">
         <v>295</v>
-      </c>
-      <c r="B177" t="s">
-        <v>296</v>
       </c>
       <c r="C177" t="s">
         <v>127</v>
@@ -16186,10 +16183,10 @@
     </row>
     <row r="178" spans="1:22">
       <c r="A178" t="s">
+        <v>294</v>
+      </c>
+      <c r="B178" t="s">
         <v>295</v>
-      </c>
-      <c r="B178" t="s">
-        <v>296</v>
       </c>
       <c r="C178" t="s">
         <v>127</v>
@@ -16248,7 +16245,7 @@
     </row>
     <row r="179" spans="1:22">
       <c r="A179" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="180" spans="1:22">
@@ -16321,10 +16318,10 @@
     </row>
     <row r="181" spans="1:22">
       <c r="A181" t="s">
+        <v>297</v>
+      </c>
+      <c r="B181" t="s">
         <v>298</v>
-      </c>
-      <c r="B181" t="s">
-        <v>299</v>
       </c>
       <c r="C181" t="s">
         <v>124</v>
@@ -16372,10 +16369,10 @@
     </row>
     <row r="182" spans="1:22">
       <c r="A182" t="s">
+        <v>297</v>
+      </c>
+      <c r="B182" t="s">
         <v>298</v>
-      </c>
-      <c r="B182" t="s">
-        <v>299</v>
       </c>
       <c r="C182" t="s">
         <v>124</v>
@@ -16415,10 +16412,10 @@
     </row>
     <row r="183" spans="1:22">
       <c r="A183" t="s">
+        <v>299</v>
+      </c>
+      <c r="B183" t="s">
         <v>300</v>
-      </c>
-      <c r="B183" t="s">
-        <v>301</v>
       </c>
       <c r="C183" t="s">
         <v>115</v>
@@ -16483,10 +16480,10 @@
     </row>
     <row r="184" spans="1:22">
       <c r="A184" t="s">
+        <v>299</v>
+      </c>
+      <c r="B184" t="s">
         <v>300</v>
-      </c>
-      <c r="B184" t="s">
-        <v>301</v>
       </c>
       <c r="C184" t="s">
         <v>115</v>
@@ -16541,16 +16538,16 @@
     </row>
     <row r="185" spans="1:22">
       <c r="A185" t="s">
+        <v>301</v>
+      </c>
+      <c r="B185" t="s">
         <v>302</v>
-      </c>
-      <c r="B185" t="s">
-        <v>303</v>
       </c>
       <c r="C185" t="s">
         <v>127</v>
       </c>
       <c r="D185" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E185" t="s">
         <v>60</v>
@@ -16609,16 +16606,16 @@
     </row>
     <row r="186" spans="1:22">
       <c r="A186" t="s">
+        <v>301</v>
+      </c>
+      <c r="B186" t="s">
         <v>302</v>
-      </c>
-      <c r="B186" t="s">
-        <v>303</v>
       </c>
       <c r="C186" t="s">
         <v>127</v>
       </c>
       <c r="D186" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E186" t="s">
         <v>60</v>
@@ -16661,10 +16658,10 @@
     </row>
     <row r="187" spans="1:22">
       <c r="A187" t="s">
+        <v>304</v>
+      </c>
+      <c r="B187" t="s">
         <v>305</v>
-      </c>
-      <c r="B187" t="s">
-        <v>306</v>
       </c>
       <c r="C187" t="s">
         <v>127</v>
@@ -16729,10 +16726,10 @@
     </row>
     <row r="188" spans="1:22">
       <c r="A188" t="s">
+        <v>304</v>
+      </c>
+      <c r="B188" t="s">
         <v>305</v>
-      </c>
-      <c r="B188" t="s">
-        <v>306</v>
       </c>
       <c r="C188" t="s">
         <v>127</v>
@@ -16781,10 +16778,10 @@
     </row>
     <row r="189" spans="1:22">
       <c r="A189" t="s">
+        <v>306</v>
+      </c>
+      <c r="B189" t="s">
         <v>307</v>
-      </c>
-      <c r="B189" t="s">
-        <v>308</v>
       </c>
       <c r="C189" t="s">
         <v>127</v>
@@ -16849,10 +16846,10 @@
     </row>
     <row r="190" spans="1:22">
       <c r="A190" t="s">
+        <v>306</v>
+      </c>
+      <c r="B190" t="s">
         <v>307</v>
-      </c>
-      <c r="B190" t="s">
-        <v>308</v>
       </c>
       <c r="C190" t="s">
         <v>127</v>
@@ -16893,16 +16890,16 @@
     </row>
     <row r="191" spans="1:22">
       <c r="A191" t="s">
+        <v>308</v>
+      </c>
+      <c r="B191" t="s">
         <v>309</v>
-      </c>
-      <c r="B191" t="s">
-        <v>310</v>
       </c>
       <c r="C191" t="s">
         <v>127</v>
       </c>
       <c r="D191" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E191" t="s">
         <v>29</v>
@@ -16961,16 +16958,16 @@
     </row>
     <row r="192" spans="1:22">
       <c r="A192" t="s">
+        <v>308</v>
+      </c>
+      <c r="B192" t="s">
         <v>309</v>
-      </c>
-      <c r="B192" t="s">
-        <v>310</v>
       </c>
       <c r="C192" t="s">
         <v>127</v>
       </c>
       <c r="D192" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E192" t="s">
         <v>29</v>
@@ -17019,16 +17016,16 @@
     </row>
     <row r="193" spans="1:22">
       <c r="A193" t="s">
+        <v>311</v>
+      </c>
+      <c r="B193" t="s">
         <v>312</v>
-      </c>
-      <c r="B193" t="s">
-        <v>313</v>
       </c>
       <c r="C193" t="s">
         <v>127</v>
       </c>
       <c r="D193" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E193" t="s">
         <v>29</v>
@@ -17071,16 +17068,16 @@
     </row>
     <row r="194" spans="1:22">
       <c r="A194" t="s">
+        <v>311</v>
+      </c>
+      <c r="B194" t="s">
         <v>312</v>
-      </c>
-      <c r="B194" t="s">
-        <v>313</v>
       </c>
       <c r="C194" t="s">
         <v>127</v>
       </c>
       <c r="D194" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E194" t="s">
         <v>29</v>
@@ -17117,10 +17114,10 @@
     </row>
     <row r="195" spans="1:22">
       <c r="A195" t="s">
+        <v>314</v>
+      </c>
+      <c r="B195" t="s">
         <v>315</v>
-      </c>
-      <c r="B195" t="s">
-        <v>316</v>
       </c>
       <c r="C195" t="s">
         <v>124</v>
@@ -17169,10 +17166,10 @@
     </row>
     <row r="196" spans="1:22">
       <c r="A196" t="s">
+        <v>314</v>
+      </c>
+      <c r="B196" t="s">
         <v>315</v>
-      </c>
-      <c r="B196" t="s">
-        <v>316</v>
       </c>
       <c r="C196" t="s">
         <v>124</v>
@@ -17213,10 +17210,10 @@
     </row>
     <row r="197" spans="1:22">
       <c r="A197" t="s">
+        <v>316</v>
+      </c>
+      <c r="B197" t="s">
         <v>317</v>
-      </c>
-      <c r="B197" t="s">
-        <v>318</v>
       </c>
       <c r="C197" t="s">
         <v>124</v>
@@ -17281,10 +17278,10 @@
     </row>
     <row r="198" spans="1:22">
       <c r="A198" t="s">
+        <v>316</v>
+      </c>
+      <c r="B198" t="s">
         <v>317</v>
-      </c>
-      <c r="B198" t="s">
-        <v>318</v>
       </c>
       <c r="C198" t="s">
         <v>124</v>
@@ -17325,10 +17322,10 @@
     </row>
     <row r="199" spans="1:22">
       <c r="A199" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B199" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C199" t="s">
         <v>124</v>
@@ -17393,10 +17390,10 @@
     </row>
     <row r="200" spans="1:22">
       <c r="A200" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B200" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C200" t="s">
         <v>124</v>
@@ -17470,26 +17467,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17627,18 +17604,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2659" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A42A162-746F-45BA-AED8-0C293C658E02}"/>
+  <xr:revisionPtr revIDLastSave="2662" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{926637B1-4E01-4448-993C-82ED5AED2257}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7150,7 +7150,9 @@
       <c r="Q28" s="12">
         <v>0.66666666666666696</v>
       </c>
-      <c r="R28" s="12"/>
+      <c r="R28" s="12">
+        <v>0.8</v>
+      </c>
       <c r="S28" s="12"/>
       <c r="T28" s="12"/>
       <c r="U28" s="12" t="s">
@@ -7540,7 +7542,9 @@
       <c r="Q34" s="12">
         <v>1</v>
       </c>
-      <c r="R34" s="12"/>
+      <c r="R34" s="12">
+        <v>0.6</v>
+      </c>
       <c r="S34" s="12"/>
       <c r="T34" s="12"/>
       <c r="U34" s="12" t="s">
@@ -7758,7 +7762,9 @@
       <c r="Q38" s="12">
         <v>0.88888888888888895</v>
       </c>
-      <c r="R38" s="12"/>
+      <c r="R38" s="12">
+        <v>0.71428571428571397</v>
+      </c>
       <c r="S38" s="12"/>
       <c r="T38" s="12"/>
       <c r="U38" s="12" t="s">
@@ -17467,6 +17473,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17604,38 +17630,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2662" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{926637B1-4E01-4448-993C-82ED5AED2257}"/>
+  <xr:revisionPtr revIDLastSave="2669" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61A153D0-87F2-47EF-8572-33171403E23A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7020,7 +7020,9 @@
       <c r="Q26" s="12">
         <v>0</v>
       </c>
-      <c r="R26" s="12"/>
+      <c r="R26" s="12">
+        <v>0</v>
+      </c>
       <c r="S26" s="12"/>
       <c r="T26" s="12"/>
       <c r="U26" s="12" t="s">
@@ -7148,10 +7150,10 @@
         <v>1</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.66666666666666696</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="R28" s="12">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S28" s="12"/>
       <c r="T28" s="12"/>
@@ -7282,7 +7284,9 @@
       <c r="Q30" s="12">
         <v>0.974683544303797</v>
       </c>
-      <c r="R30" s="12"/>
+      <c r="R30" s="12">
+        <v>1</v>
+      </c>
       <c r="S30" s="12"/>
       <c r="T30" s="12"/>
       <c r="U30" s="12" t="s">
@@ -7412,7 +7416,9 @@
       <c r="Q32" s="12">
         <v>1</v>
       </c>
-      <c r="R32" s="12"/>
+      <c r="R32" s="12">
+        <v>1</v>
+      </c>
       <c r="S32" s="12"/>
       <c r="T32" s="12"/>
       <c r="U32" s="12" t="s">
@@ -7543,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="R34" s="12">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="S34" s="12"/>
       <c r="T34" s="12"/>
@@ -7763,7 +7769,7 @@
         <v>0.88888888888888895</v>
       </c>
       <c r="R38" s="12">
-        <v>0.71428571428571397</v>
+        <v>1</v>
       </c>
       <c r="S38" s="12"/>
       <c r="T38" s="12"/>
@@ -17479,20 +17485,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17630,12 +17622,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17643,5 +17649,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>